--- a/Financial Analysis/HRMS.xlsx
+++ b/Financial Analysis/HRMS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5F46E2-2194-4012-9B79-747CF1B5D740}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA49C43-7E92-40A9-8A80-93C3D153F9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C4BF79F1-8F77-4375-9B67-0BA0B548E64B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>HRMS</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
     <t>H121</t>
   </si>
   <si>
@@ -164,6 +161,36 @@
   </si>
   <si>
     <t>Operating y/y</t>
+  </si>
+  <si>
+    <t>H122</t>
+  </si>
+  <si>
+    <t>H222</t>
+  </si>
+  <si>
+    <t>H123</t>
+  </si>
+  <si>
+    <t>H223</t>
+  </si>
+  <si>
+    <t>H124</t>
+  </si>
+  <si>
+    <t>H224</t>
+  </si>
+  <si>
+    <t>H125</t>
+  </si>
+  <si>
+    <t>H225</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -218,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -234,10 +261,9 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -285,6 +311,106 @@
         <a:xfrm>
           <a:off x="5814060" y="0"/>
           <a:ext cx="0" cy="6103620"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{480B6B79-757D-DDD9-BCB5-27EA938D22BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16779240" y="0"/>
+          <a:ext cx="0" cy="5707380"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1105CEF8-766A-A17E-D720-75FFAFB34BE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11285220" y="7620"/>
+          <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -633,17 +759,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>1049.08</v>
+        <v>2071</v>
       </c>
       <c r="E3" s="3">
-        <v>44312</v>
+        <v>45965</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>44312</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="3">
-        <v>44407</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -651,10 +777,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>105.569</v>
+        <v>105.6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -663,7 +789,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>110750.32651999999</v>
+        <v>218697.59999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -671,11 +797,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>4732.7+48.8</f>
-        <v>4781.5</v>
+        <f>10321+229</f>
+        <v>10550</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -683,11 +809,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>18.4+24.5</f>
-        <v>42.9</v>
+        <f>2+30</f>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -696,7 +822,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>4738.6000000000004</v>
+        <v>10518</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -705,7 +831,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>106011.72651999998</v>
+        <v>208179.59999999998</v>
       </c>
     </row>
   </sheetData>
@@ -715,15 +841,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78774AD-DD33-4B7E-8233-5E79767483A9}">
-  <dimension ref="B2:EV27"/>
+  <dimension ref="B2:FI27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.88671875" customWidth="1"/>
+    <col min="39" max="39" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:165" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
@@ -743,52 +870,91 @@
         <v>17</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2">
+      <c r="K2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T2">
         <v>2018</v>
       </c>
-      <c r="M2">
+      <c r="U2">
         <v>2019</v>
       </c>
-      <c r="N2">
+      <c r="V2">
         <v>2020</v>
       </c>
-      <c r="O2">
+      <c r="W2">
         <v>2021</v>
       </c>
-      <c r="P2">
+      <c r="X2">
         <v>2022</v>
       </c>
-      <c r="Q2">
+      <c r="Y2">
         <v>2023</v>
       </c>
-      <c r="R2">
+      <c r="Z2">
         <v>2024</v>
       </c>
-      <c r="S2">
+      <c r="AA2">
         <v>2025</v>
       </c>
-      <c r="T2">
+      <c r="AB2">
         <v>2026</v>
       </c>
-      <c r="U2">
+      <c r="AC2">
         <v>2027</v>
       </c>
-      <c r="V2">
+      <c r="AD2">
         <v>2028</v>
       </c>
-      <c r="W2">
+      <c r="AE2">
         <v>2029</v>
       </c>
-      <c r="X2">
+      <c r="AF2">
         <v>2030</v>
       </c>
+      <c r="AG2">
+        <v>2031</v>
+      </c>
+      <c r="AH2">
+        <v>2032</v>
+      </c>
+      <c r="AI2">
+        <v>2033</v>
+      </c>
+      <c r="AJ2">
+        <v>2034</v>
+      </c>
+      <c r="AK2">
+        <v>2035</v>
+      </c>
     </row>
-    <row r="3" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
@@ -796,14 +962,14 @@
         <v>2853</v>
       </c>
       <c r="D3" s="8">
-        <f>L3-C3</f>
+        <f>T3-C3</f>
         <v>3113.1000000000004</v>
       </c>
       <c r="E3" s="8">
         <v>3284.2</v>
       </c>
       <c r="F3" s="8">
-        <f>M3-E3</f>
+        <f>U3-E3</f>
         <v>3599.2</v>
       </c>
       <c r="G3" s="8">
@@ -814,81 +980,123 @@
         <v>3901.3999999999996</v>
       </c>
       <c r="I3" s="8">
-        <f>G3*1.32</f>
-        <v>3284.1600000000003</v>
+        <v>4235.1000000000004</v>
       </c>
       <c r="J3" s="8">
-        <f>H3*1.15</f>
-        <v>4486.6099999999997</v>
-      </c>
-      <c r="K3" s="12"/>
+        <f>W3-I3</f>
+        <v>4746.8999999999996</v>
+      </c>
+      <c r="K3" s="8">
+        <v>5475</v>
+      </c>
       <c r="L3" s="8">
+        <f>X3-K3</f>
+        <v>6127</v>
+      </c>
+      <c r="M3" s="8">
+        <v>6698</v>
+      </c>
+      <c r="N3" s="8">
+        <f>Y3-M3</f>
+        <v>6729</v>
+      </c>
+      <c r="O3" s="8">
+        <v>7504</v>
+      </c>
+      <c r="P3" s="8">
+        <f>Z3-O3</f>
+        <v>7666</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>8034</v>
+      </c>
+      <c r="R3" s="8">
+        <f>P3*1.06</f>
+        <v>8125.96</v>
+      </c>
+      <c r="S3" s="10"/>
+      <c r="T3" s="8">
         <v>5966.1</v>
       </c>
-      <c r="M3" s="8">
+      <c r="U3" s="8">
         <v>6883.4</v>
       </c>
-      <c r="N3" s="8">
-        <f>SUM(G3:H3)</f>
+      <c r="V3" s="8">
         <v>6389.4</v>
       </c>
-      <c r="O3" s="8">
-        <f>SUM(I3:J3)</f>
-        <v>7770.77</v>
-      </c>
-      <c r="P3" s="8">
-        <f>O3*1.16</f>
-        <v>9014.0931999999993</v>
-      </c>
-      <c r="Q3" s="8">
-        <f>P3*1.12</f>
-        <v>10095.784384000001</v>
-      </c>
-      <c r="R3" s="8">
-        <f>Q3*1.09</f>
-        <v>11004.404978560002</v>
-      </c>
-      <c r="S3" s="8">
-        <f>R3*1.06</f>
-        <v>11664.669277273602</v>
-      </c>
-      <c r="T3" s="8">
-        <f>S3*1.05</f>
-        <v>12247.902741137283</v>
-      </c>
-      <c r="U3" s="8">
-        <f>T3*1.05</f>
-        <v>12860.297878194147</v>
-      </c>
-      <c r="V3" s="8">
-        <f>U3*1.04</f>
-        <v>13374.709793321914</v>
-      </c>
       <c r="W3" s="8">
-        <f t="shared" ref="W3:X3" si="0">V3*1.03</f>
-        <v>13775.951087121572</v>
+        <v>8982</v>
       </c>
       <c r="X3" s="8">
+        <v>11602</v>
+      </c>
+      <c r="Y3" s="8">
+        <v>13427</v>
+      </c>
+      <c r="Z3" s="8">
+        <v>15170</v>
+      </c>
+      <c r="AA3" s="8">
+        <f>SUM(Q3:R3)</f>
+        <v>16159.96</v>
+      </c>
+      <c r="AB3" s="8">
+        <f>AA3*1.06</f>
+        <v>17129.5576</v>
+      </c>
+      <c r="AC3" s="8">
+        <f>AB3*1.05</f>
+        <v>17986.035480000002</v>
+      </c>
+      <c r="AD3" s="8">
+        <f>AC3*1.04</f>
+        <v>18705.476899200003</v>
+      </c>
+      <c r="AE3" s="8">
+        <f t="shared" ref="AE3:AF3" si="0">AD3*1.03</f>
+        <v>19266.641206176002</v>
+      </c>
+      <c r="AF3" s="8">
         <f t="shared" si="0"/>
-        <v>14189.229619735219</v>
+        <v>19844.640442361284</v>
+      </c>
+      <c r="AG3" s="8">
+        <f t="shared" ref="AG3" si="1">AF3*1.03</f>
+        <v>20439.979655632123</v>
+      </c>
+      <c r="AH3" s="8">
+        <f t="shared" ref="AH3" si="2">AG3*1.03</f>
+        <v>21053.179045301087</v>
+      </c>
+      <c r="AI3" s="8">
+        <f t="shared" ref="AI3" si="3">AH3*1.03</f>
+        <v>21684.774416660119</v>
+      </c>
+      <c r="AJ3" s="8">
+        <f t="shared" ref="AJ3" si="4">AI3*1.03</f>
+        <v>22335.317649159922</v>
+      </c>
+      <c r="AK3" s="8">
+        <f t="shared" ref="AK3" si="5">AJ3*1.03</f>
+        <v>23005.377178634721</v>
       </c>
     </row>
-    <row r="4" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:165" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="5">
         <v>859</v>
       </c>
-      <c r="D4" s="9">
-        <f>L4-C4</f>
+      <c r="D4" s="5">
+        <f>T4-C4</f>
         <v>932.8</v>
       </c>
       <c r="E4" s="5">
         <v>1029.0999999999999</v>
       </c>
-      <c r="F4" s="9">
-        <f>M4-E4</f>
+      <c r="F4" s="5">
+        <f>U4-E4</f>
         <v>1095.8000000000002</v>
       </c>
       <c r="G4" s="5">
@@ -899,154 +1107,248 @@
         <v>1142.5999999999999</v>
       </c>
       <c r="I4" s="5">
-        <f>I3-I5</f>
-        <v>985.24800000000005</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" ref="J4" si="1">J3-J5</f>
-        <v>1345.9830000000002</v>
-      </c>
-      <c r="L4" s="5">
+        <v>1207.2</v>
+      </c>
+      <c r="J4" s="11">
+        <f>W4-I4</f>
+        <v>1372.8</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1586</v>
+      </c>
+      <c r="L4" s="11">
+        <f>X4-K4</f>
+        <v>1803</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1863</v>
+      </c>
+      <c r="N4" s="11">
+        <f>Y4-M4</f>
+        <v>1857</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2206</v>
+      </c>
+      <c r="P4" s="11">
+        <f>Z4-O4</f>
+        <v>2305</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>2356</v>
+      </c>
+      <c r="R4" s="5">
+        <f>R3-R5</f>
+        <v>2437.7880000000005</v>
+      </c>
+      <c r="T4" s="5">
         <v>1791.8</v>
       </c>
-      <c r="M4" s="5">
+      <c r="U4" s="5">
         <v>2124.9</v>
       </c>
-      <c r="N4" s="9">
-        <f>SUM(G4:H4)</f>
+      <c r="V4" s="5">
         <v>2013.3</v>
       </c>
-      <c r="O4" s="9">
-        <f>SUM(I4:J4)</f>
-        <v>2331.2310000000002</v>
-      </c>
-      <c r="P4" s="5">
-        <f t="shared" ref="P4:X4" si="2">P3-P5</f>
-        <v>2704.2279600000002</v>
-      </c>
-      <c r="Q4" s="5">
-        <f t="shared" si="2"/>
-        <v>3028.7353152000005</v>
-      </c>
-      <c r="R4" s="5">
-        <f t="shared" si="2"/>
-        <v>3301.3214935680007</v>
-      </c>
-      <c r="S4" s="5">
-        <f t="shared" si="2"/>
-        <v>3499.4007831820809</v>
-      </c>
-      <c r="T4" s="5">
-        <f t="shared" si="2"/>
-        <v>3674.370822341185</v>
-      </c>
-      <c r="U4" s="5">
-        <f t="shared" si="2"/>
-        <v>3858.0893634582444</v>
-      </c>
-      <c r="V4" s="5">
-        <f t="shared" si="2"/>
-        <v>4012.4129379965743</v>
-      </c>
       <c r="W4" s="5">
-        <f t="shared" si="2"/>
-        <v>4132.7853261364726</v>
+        <v>2580</v>
       </c>
       <c r="X4" s="5">
-        <f t="shared" si="2"/>
-        <v>4256.7688859205664</v>
+        <v>3389</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>3720</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>4511</v>
+      </c>
+      <c r="AA4" s="11">
+        <f>SUM(Q4:R4)</f>
+        <v>4793.7880000000005</v>
+      </c>
+      <c r="AB4" s="5">
+        <f t="shared" ref="X4:AF4" si="6">AB3-AB5</f>
+        <v>5138.8672800000004</v>
+      </c>
+      <c r="AC4" s="5">
+        <f t="shared" si="6"/>
+        <v>5395.810644000001</v>
+      </c>
+      <c r="AD4" s="5">
+        <f t="shared" si="6"/>
+        <v>5611.6430697600008</v>
+      </c>
+      <c r="AE4" s="5">
+        <f t="shared" si="6"/>
+        <v>5779.992361852801</v>
+      </c>
+      <c r="AF4" s="5">
+        <f t="shared" si="6"/>
+        <v>5953.3921327083863</v>
+      </c>
+      <c r="AG4" s="5">
+        <f t="shared" ref="AG4:AK4" si="7">AG3-AG5</f>
+        <v>6131.993896689637</v>
+      </c>
+      <c r="AH4" s="5">
+        <f t="shared" si="7"/>
+        <v>6315.9537135903265</v>
+      </c>
+      <c r="AI4" s="5">
+        <f t="shared" si="7"/>
+        <v>6505.4323249980371</v>
+      </c>
+      <c r="AJ4" s="5">
+        <f t="shared" si="7"/>
+        <v>6700.5952947479782</v>
+      </c>
+      <c r="AK4" s="5">
+        <f t="shared" si="7"/>
+        <v>6901.6131535904169</v>
       </c>
     </row>
-    <row r="5" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:H5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:I5" si="8">C3-C4</f>
         <v>1994</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2180.3000000000002</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2255.1</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2503.3999999999996</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1617.3</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2758.7999999999997</v>
       </c>
       <c r="I5" s="8">
-        <f>I3*0.7</f>
-        <v>2298.9120000000003</v>
+        <f t="shared" si="8"/>
+        <v>3027.9000000000005</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" ref="J5" si="4">J3*0.7</f>
-        <v>3140.6269999999995</v>
+        <f t="shared" ref="J5" si="9">J3-J4</f>
+        <v>3374.0999999999995</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" ref="K5:L5" si="10">K3-K4</f>
+        <v>3889</v>
       </c>
       <c r="L5" s="8">
-        <f>L3-L4</f>
+        <f t="shared" si="10"/>
+        <v>4324</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" ref="M5:N5" si="11">M3-M4</f>
+        <v>4835</v>
+      </c>
+      <c r="N5" s="8">
+        <f t="shared" si="11"/>
+        <v>4872</v>
+      </c>
+      <c r="O5" s="8">
+        <f t="shared" ref="O5:Q5" si="12">O3-O4</f>
+        <v>5298</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" ref="P5" si="13">P3-P4</f>
+        <v>5361</v>
+      </c>
+      <c r="Q5" s="8">
+        <f t="shared" si="12"/>
+        <v>5678</v>
+      </c>
+      <c r="R5" s="8">
+        <f>R3*0.7</f>
+        <v>5688.1719999999996</v>
+      </c>
+      <c r="T5" s="8">
+        <f>T3-T4</f>
         <v>4174.3</v>
       </c>
-      <c r="M5" s="8">
-        <f>M3-M4</f>
+      <c r="U5" s="8">
+        <f>U3-U4</f>
         <v>4758.5</v>
       </c>
-      <c r="N5" s="8">
-        <f>N3-N4</f>
+      <c r="V5" s="8">
+        <f>V3-V4</f>
         <v>4376.0999999999995</v>
       </c>
-      <c r="O5" s="8">
-        <f>O3-O4</f>
-        <v>5439.5390000000007</v>
-      </c>
-      <c r="P5" s="8">
-        <f t="shared" ref="P5:X5" si="5">P3*0.7</f>
-        <v>6309.8652399999992</v>
-      </c>
-      <c r="Q5" s="8">
-        <f t="shared" si="5"/>
-        <v>7067.0490688</v>
-      </c>
-      <c r="R5" s="8">
-        <f t="shared" si="5"/>
-        <v>7703.0834849920011</v>
-      </c>
-      <c r="S5" s="8">
-        <f t="shared" si="5"/>
-        <v>8165.2684940915215</v>
-      </c>
-      <c r="T5" s="8">
-        <f t="shared" si="5"/>
-        <v>8573.5319187960977</v>
-      </c>
-      <c r="U5" s="8">
-        <f t="shared" si="5"/>
-        <v>9002.208514735903</v>
-      </c>
-      <c r="V5" s="8">
-        <f t="shared" si="5"/>
-        <v>9362.2968553253395</v>
-      </c>
       <c r="W5" s="8">
-        <f t="shared" si="5"/>
-        <v>9643.165760985099</v>
+        <f t="shared" ref="W5:X5" si="14">W3-W4</f>
+        <v>6402</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="5"/>
-        <v>9932.4607338146525</v>
+        <f t="shared" si="14"/>
+        <v>8213</v>
+      </c>
+      <c r="Y5" s="8">
+        <f t="shared" ref="Y5:Z5" si="15">Y3-Y4</f>
+        <v>9707</v>
+      </c>
+      <c r="Z5" s="8">
+        <f t="shared" si="15"/>
+        <v>10659</v>
+      </c>
+      <c r="AA5" s="8">
+        <f t="shared" ref="X5:AF5" si="16">AA3*0.7</f>
+        <v>11311.971999999998</v>
+      </c>
+      <c r="AB5" s="8">
+        <f t="shared" si="16"/>
+        <v>11990.69032</v>
+      </c>
+      <c r="AC5" s="8">
+        <f t="shared" si="16"/>
+        <v>12590.224836000001</v>
+      </c>
+      <c r="AD5" s="8">
+        <f t="shared" si="16"/>
+        <v>13093.833829440002</v>
+      </c>
+      <c r="AE5" s="8">
+        <f t="shared" si="16"/>
+        <v>13486.648844323201</v>
+      </c>
+      <c r="AF5" s="8">
+        <f t="shared" si="16"/>
+        <v>13891.248309652898</v>
+      </c>
+      <c r="AG5" s="8">
+        <f t="shared" ref="AG5:AK5" si="17">AG3*0.7</f>
+        <v>14307.985758942486</v>
+      </c>
+      <c r="AH5" s="8">
+        <f t="shared" si="17"/>
+        <v>14737.225331710761</v>
+      </c>
+      <c r="AI5" s="8">
+        <f t="shared" si="17"/>
+        <v>15179.342091662082</v>
+      </c>
+      <c r="AJ5" s="8">
+        <f t="shared" si="17"/>
+        <v>15634.722354411944</v>
+      </c>
+      <c r="AK5" s="8">
+        <f t="shared" si="17"/>
+        <v>16103.764025044304</v>
       </c>
     </row>
-    <row r="6" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:165" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -1054,15 +1356,15 @@
         <f>120+611</f>
         <v>731</v>
       </c>
-      <c r="D6" s="9">
-        <f>L6-C6</f>
+      <c r="D6" s="5">
+        <f>T6-C6</f>
         <v>831.3</v>
       </c>
       <c r="E6" s="5">
         <v>842.2</v>
       </c>
-      <c r="F6" s="9">
-        <f>M6-E6</f>
+      <c r="F6" s="5">
+        <f>U6-E6</f>
         <v>973.5</v>
       </c>
       <c r="G6" s="5">
@@ -1073,65 +1375,107 @@
         <v>930</v>
       </c>
       <c r="I6" s="5">
-        <f>G6*1.1</f>
-        <v>845.35</v>
-      </c>
-      <c r="J6" s="5">
-        <f>H6*1.1</f>
-        <v>1023.0000000000001</v>
-      </c>
-      <c r="L6" s="5">
+        <v>935</v>
+      </c>
+      <c r="J6" s="11">
+        <f t="shared" ref="J6:J7" si="18">W6-I6</f>
+        <v>1202</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1178</v>
+      </c>
+      <c r="L6" s="11">
+        <f t="shared" ref="L6:L7" si="19">X6-K6</f>
+        <v>1502</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1485</v>
+      </c>
+      <c r="N6" s="11">
+        <f t="shared" ref="N6:N7" si="20">Y6-M6</f>
+        <v>1684</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1682</v>
+      </c>
+      <c r="P6" s="11">
+        <f t="shared" ref="P6:P7" si="21">Z6-O6</f>
+        <v>1887</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>1832</v>
+      </c>
+      <c r="R6" s="5">
+        <f>P6*1.08</f>
+        <v>2037.96</v>
+      </c>
+      <c r="T6" s="5">
         <v>1562.3</v>
       </c>
-      <c r="M6" s="5">
+      <c r="U6" s="5">
         <v>1815.7</v>
       </c>
-      <c r="N6" s="9">
-        <f>SUM(G6:H6)</f>
+      <c r="V6" s="5">
         <v>1698.5</v>
       </c>
-      <c r="O6" s="9">
-        <f>SUM(I6:J6)</f>
-        <v>1868.3500000000001</v>
-      </c>
-      <c r="P6" s="5">
-        <f>O6*1.08</f>
-        <v>2017.8180000000002</v>
-      </c>
-      <c r="Q6" s="5">
-        <f>P6*1.06</f>
-        <v>2138.8870800000004</v>
-      </c>
-      <c r="R6" s="5">
-        <f>Q6*1.05</f>
-        <v>2245.8314340000006</v>
-      </c>
-      <c r="S6" s="5">
-        <f t="shared" ref="S6" si="6">R6*1.03</f>
-        <v>2313.2063770200007</v>
-      </c>
-      <c r="T6" s="5">
-        <f t="shared" ref="T6" si="7">S6*1.03</f>
-        <v>2382.6025683306007</v>
-      </c>
-      <c r="U6" s="5">
-        <f>T6*1.02</f>
-        <v>2430.2546196972125</v>
-      </c>
-      <c r="V6" s="5">
-        <f t="shared" ref="V6:X6" si="8">U6*1.02</f>
-        <v>2478.8597120911568</v>
-      </c>
       <c r="W6" s="5">
-        <f t="shared" si="8"/>
-        <v>2528.43690633298</v>
+        <v>2137</v>
       </c>
       <c r="X6" s="5">
-        <f t="shared" si="8"/>
-        <v>2579.0056444596398</v>
+        <v>2680</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>3169</v>
+      </c>
+      <c r="Z6" s="5">
+        <v>3569</v>
+      </c>
+      <c r="AA6" s="11">
+        <f t="shared" ref="AA6:AA7" si="22">SUM(Q6:R6)</f>
+        <v>3869.96</v>
+      </c>
+      <c r="AB6" s="5">
+        <f t="shared" ref="AB6" si="23">AA6*1.03</f>
+        <v>3986.0588000000002</v>
+      </c>
+      <c r="AC6" s="5">
+        <f>AB6*1.02</f>
+        <v>4065.7799760000003</v>
+      </c>
+      <c r="AD6" s="5">
+        <f t="shared" ref="AD6:AF6" si="24">AC6*1.02</f>
+        <v>4147.0955755200002</v>
+      </c>
+      <c r="AE6" s="5">
+        <f t="shared" si="24"/>
+        <v>4230.0374870304004</v>
+      </c>
+      <c r="AF6" s="5">
+        <f t="shared" si="24"/>
+        <v>4314.6382367710085</v>
+      </c>
+      <c r="AG6" s="5">
+        <f t="shared" ref="AG6:AG7" si="25">AF6*1.02</f>
+        <v>4400.9310015064284</v>
+      </c>
+      <c r="AH6" s="5">
+        <f t="shared" ref="AH6:AH7" si="26">AG6*1.02</f>
+        <v>4488.9496215365571</v>
+      </c>
+      <c r="AI6" s="5">
+        <f t="shared" ref="AI6:AI7" si="27">AH6*1.02</f>
+        <v>4578.7286139672879</v>
+      </c>
+      <c r="AJ6" s="5">
+        <f t="shared" ref="AJ6:AJ7" si="28">AI6*1.02</f>
+        <v>4670.3031862466341</v>
+      </c>
+      <c r="AK6" s="5">
+        <f t="shared" ref="AK6:AK7" si="29">AJ6*1.02</f>
+        <v>4763.7092499715673</v>
       </c>
     </row>
-    <row r="7" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:165" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>21</v>
       </c>
@@ -1139,15 +1483,15 @@
         <f>267-53</f>
         <v>214</v>
       </c>
-      <c r="D7" s="9">
-        <f>L7-C7</f>
+      <c r="D7" s="5">
+        <f>T7-C7</f>
         <v>270.70000000000005</v>
       </c>
       <c r="E7" s="5">
         <v>269</v>
       </c>
-      <c r="F7" s="9">
-        <f>M7-E7</f>
+      <c r="F7" s="5">
+        <f>U7-E7</f>
         <v>335</v>
       </c>
       <c r="G7" s="5">
@@ -1158,341 +1502,532 @@
         <v>382.00000000000006</v>
       </c>
       <c r="I7" s="5">
-        <f>G7*1.13</f>
-        <v>355.04599999999994</v>
-      </c>
-      <c r="J7" s="5">
-        <f t="shared" ref="J7" si="9">H7*1.13</f>
-        <v>431.66</v>
-      </c>
-      <c r="L7" s="5">
+        <v>371.1</v>
+      </c>
+      <c r="J7" s="11">
+        <f t="shared" si="18"/>
+        <v>362.9</v>
+      </c>
+      <c r="K7" s="5">
+        <v>406</v>
+      </c>
+      <c r="L7" s="11">
+        <f t="shared" si="19"/>
+        <v>430</v>
+      </c>
+      <c r="M7" s="5">
+        <v>403</v>
+      </c>
+      <c r="N7" s="11">
+        <f t="shared" si="20"/>
+        <v>486</v>
+      </c>
+      <c r="O7" s="5">
+        <v>467</v>
+      </c>
+      <c r="P7" s="11">
+        <f t="shared" si="21"/>
+        <v>475</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>519</v>
+      </c>
+      <c r="R7" s="5">
+        <f>P7*1.1</f>
+        <v>522.5</v>
+      </c>
+      <c r="T7" s="5">
         <f>536.7-52</f>
         <v>484.70000000000005</v>
       </c>
-      <c r="M7" s="5">
+      <c r="U7" s="5">
         <v>604</v>
       </c>
-      <c r="N7" s="9">
-        <f>SUM(G7:H7)</f>
+      <c r="V7" s="5">
         <v>696.2</v>
       </c>
-      <c r="O7" s="9">
-        <f>SUM(I7:J7)</f>
-        <v>786.7059999999999</v>
-      </c>
-      <c r="P7" s="5">
-        <f>O7*1.08</f>
-        <v>849.64247999999998</v>
-      </c>
-      <c r="Q7" s="5">
-        <f t="shared" ref="Q7:R7" si="10">P7*1.05</f>
-        <v>892.12460399999998</v>
-      </c>
-      <c r="R7" s="5">
-        <f t="shared" si="10"/>
-        <v>936.7308342</v>
-      </c>
-      <c r="S7" s="5">
-        <f>R7*1.04</f>
-        <v>974.20006756800001</v>
-      </c>
-      <c r="T7" s="5">
-        <f>S7*1.03</f>
-        <v>1003.4260695950401</v>
-      </c>
-      <c r="U7" s="5">
-        <f>T7*1.02</f>
-        <v>1023.4945909869409</v>
-      </c>
-      <c r="V7" s="5">
-        <f t="shared" ref="V7:X7" si="11">U7*1.02</f>
-        <v>1043.9644828066798</v>
-      </c>
       <c r="W7" s="5">
-        <f t="shared" si="11"/>
-        <v>1064.8437724628134</v>
+        <v>734</v>
       </c>
       <c r="X7" s="5">
-        <f t="shared" si="11"/>
-        <v>1086.1406479120697</v>
+        <v>836</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>889</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>942</v>
+      </c>
+      <c r="AA7" s="11">
+        <f t="shared" si="22"/>
+        <v>1041.5</v>
+      </c>
+      <c r="AB7" s="5">
+        <f>AA7*1.03</f>
+        <v>1072.7450000000001</v>
+      </c>
+      <c r="AC7" s="5">
+        <f>AB7*1.02</f>
+        <v>1094.1999000000001</v>
+      </c>
+      <c r="AD7" s="5">
+        <f t="shared" ref="AD7:AF7" si="30">AC7*1.02</f>
+        <v>1116.0838980000001</v>
+      </c>
+      <c r="AE7" s="5">
+        <f t="shared" si="30"/>
+        <v>1138.4055759600001</v>
+      </c>
+      <c r="AF7" s="5">
+        <f t="shared" si="30"/>
+        <v>1161.1736874792</v>
+      </c>
+      <c r="AG7" s="5">
+        <f t="shared" si="25"/>
+        <v>1184.3971612287839</v>
+      </c>
+      <c r="AH7" s="5">
+        <f t="shared" si="26"/>
+        <v>1208.0851044533597</v>
+      </c>
+      <c r="AI7" s="5">
+        <f t="shared" si="27"/>
+        <v>1232.2468065424268</v>
+      </c>
+      <c r="AJ7" s="5">
+        <f t="shared" si="28"/>
+        <v>1256.8917426732753</v>
+      </c>
+      <c r="AK7" s="5">
+        <f t="shared" si="29"/>
+        <v>1282.0295775267409</v>
       </c>
     </row>
-    <row r="8" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="8">
-        <f t="shared" ref="C8:J8" si="12">C5-C6-C7</f>
+        <f t="shared" ref="C8:L8" si="31">C5-C6-C7</f>
         <v>1049</v>
       </c>
       <c r="D8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="31"/>
         <v>1078.3000000000002</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="31"/>
         <v>1143.8999999999999</v>
       </c>
       <c r="F8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="31"/>
         <v>1194.8999999999996</v>
       </c>
       <c r="G8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="31"/>
         <v>534.59999999999991</v>
       </c>
       <c r="H8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="31"/>
         <v>1446.7999999999997</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" si="12"/>
-        <v>1098.5160000000005</v>
+        <f t="shared" ref="I8:J8" si="32">I5-I6-I7</f>
+        <v>1721.8000000000006</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="12"/>
-        <v>1685.9669999999994</v>
+        <f t="shared" si="32"/>
+        <v>1809.1999999999994</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="31"/>
+        <v>2305</v>
       </c>
       <c r="L8" s="8">
-        <f>L5-L6-L7</f>
+        <f t="shared" si="31"/>
+        <v>2392</v>
+      </c>
+      <c r="M8" s="8">
+        <f t="shared" ref="M8:N8" si="33">M5-M6-M7</f>
+        <v>2947</v>
+      </c>
+      <c r="N8" s="8">
+        <f t="shared" si="33"/>
+        <v>2702</v>
+      </c>
+      <c r="O8" s="8">
+        <f t="shared" ref="O8:R8" si="34">O5-O6-O7</f>
+        <v>3149</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" ref="P8" si="35">P5-P6-P7</f>
+        <v>2999</v>
+      </c>
+      <c r="Q8" s="8">
+        <f t="shared" si="34"/>
+        <v>3327</v>
+      </c>
+      <c r="R8" s="8">
+        <f t="shared" si="34"/>
+        <v>3127.7119999999995</v>
+      </c>
+      <c r="T8" s="8">
+        <f>T5-T6-T7</f>
         <v>2127.3000000000002</v>
       </c>
-      <c r="M8" s="8">
-        <f>M5-M6-M7</f>
+      <c r="U8" s="8">
+        <f>U5-U6-U7</f>
         <v>2338.8000000000002</v>
       </c>
-      <c r="N8" s="8">
-        <f>N5-N6-N7</f>
+      <c r="V8" s="8">
+        <f>V5-V6-V7</f>
         <v>1981.3999999999994</v>
       </c>
-      <c r="O8" s="8">
-        <f t="shared" ref="O8:X8" si="13">O5-O6-O7</f>
-        <v>2784.4830000000002</v>
-      </c>
-      <c r="P8" s="8">
-        <f t="shared" si="13"/>
-        <v>3442.404759999999</v>
-      </c>
-      <c r="Q8" s="8">
-        <f t="shared" si="13"/>
-        <v>4036.0373847999995</v>
-      </c>
-      <c r="R8" s="8">
-        <f t="shared" si="13"/>
-        <v>4520.5212167920008</v>
-      </c>
-      <c r="S8" s="8">
-        <f t="shared" si="13"/>
-        <v>4877.8620495035202</v>
-      </c>
-      <c r="T8" s="8">
-        <f t="shared" si="13"/>
-        <v>5187.5032808704573</v>
-      </c>
-      <c r="U8" s="8">
-        <f t="shared" si="13"/>
-        <v>5548.4593040517493</v>
-      </c>
-      <c r="V8" s="8">
-        <f t="shared" si="13"/>
-        <v>5839.4726604275038</v>
-      </c>
       <c r="W8" s="8">
-        <f t="shared" si="13"/>
-        <v>6049.8850821893066</v>
+        <f t="shared" ref="W8" si="36">W5-W6-W7</f>
+        <v>3531</v>
       </c>
       <c r="X8" s="8">
-        <f t="shared" si="13"/>
-        <v>6267.3144414429435</v>
+        <f t="shared" ref="X8:Y8" si="37">X5-X6-X7</f>
+        <v>4697</v>
+      </c>
+      <c r="Y8" s="8">
+        <f t="shared" si="37"/>
+        <v>5649</v>
+      </c>
+      <c r="Z8" s="8">
+        <f t="shared" ref="W8:AF8" si="38">Z5-Z6-Z7</f>
+        <v>6148</v>
+      </c>
+      <c r="AA8" s="8">
+        <f t="shared" si="38"/>
+        <v>6400.5119999999979</v>
+      </c>
+      <c r="AB8" s="8">
+        <f t="shared" si="38"/>
+        <v>6931.8865199999991</v>
+      </c>
+      <c r="AC8" s="8">
+        <f t="shared" si="38"/>
+        <v>7430.2449600000018</v>
+      </c>
+      <c r="AD8" s="8">
+        <f t="shared" si="38"/>
+        <v>7830.6543559200009</v>
+      </c>
+      <c r="AE8" s="8">
+        <f t="shared" si="38"/>
+        <v>8118.2057813328011</v>
+      </c>
+      <c r="AF8" s="8">
+        <f t="shared" si="38"/>
+        <v>8415.4363854026888</v>
+      </c>
+      <c r="AG8" s="8">
+        <f t="shared" ref="AG8:AK8" si="39">AG5-AG6-AG7</f>
+        <v>8722.6575962072729</v>
+      </c>
+      <c r="AH8" s="8">
+        <f t="shared" si="39"/>
+        <v>9040.1906057208435</v>
+      </c>
+      <c r="AI8" s="8">
+        <f t="shared" si="39"/>
+        <v>9368.3666711523674</v>
+      </c>
+      <c r="AJ8" s="8">
+        <f t="shared" si="39"/>
+        <v>9707.527425492035</v>
+      </c>
+      <c r="AK8" s="8">
+        <f t="shared" si="39"/>
+        <v>10058.025197545996</v>
       </c>
     </row>
-    <row r="9" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:165" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="5">
         <v>18</v>
       </c>
-      <c r="D9" s="9">
-        <f>L9-C9</f>
+      <c r="D9" s="5">
+        <f>T9-C9</f>
         <v>43.8</v>
       </c>
       <c r="E9" s="5">
         <v>16.3</v>
       </c>
-      <c r="F9" s="9">
-        <f>M9-E9</f>
+      <c r="F9" s="5">
+        <f>U9-E9</f>
         <v>52.3</v>
       </c>
       <c r="G9" s="5">
         <v>43.4</v>
       </c>
       <c r="H9" s="5">
-        <f>-86.1+91.1-G9</f>
-        <v>-38.4</v>
+        <f>86.1-91.1-G9</f>
+        <v>-48.4</v>
       </c>
       <c r="I9" s="5">
-        <v>40</v>
-      </c>
-      <c r="J9" s="5">
-        <v>37</v>
-      </c>
-      <c r="L9" s="5">
+        <v>47</v>
+      </c>
+      <c r="J9" s="11">
+        <f>W9-I9</f>
+        <v>49</v>
+      </c>
+      <c r="K9" s="5">
+        <v>35</v>
+      </c>
+      <c r="L9" s="11">
+        <f>X9-K9</f>
+        <v>27</v>
+      </c>
+      <c r="M9" s="5">
+        <v>-75</v>
+      </c>
+      <c r="N9" s="11">
+        <f>Y9-M9</f>
+        <v>-115</v>
+      </c>
+      <c r="O9" s="5">
+        <v>-141</v>
+      </c>
+      <c r="P9" s="11">
+        <f>Z9-O9</f>
+        <v>-142</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>-148</v>
+      </c>
+      <c r="R9" s="5">
+        <f>P9*1.05</f>
+        <v>-149.1</v>
+      </c>
+      <c r="T9" s="5">
         <v>61.8</v>
       </c>
-      <c r="M9" s="5">
+      <c r="U9" s="5">
         <v>68.599999999999994</v>
       </c>
-      <c r="N9" s="9">
-        <f>SUM(G9:H9)</f>
-        <v>5</v>
-      </c>
-      <c r="O9" s="9">
-        <f>SUM(I9:J9)</f>
-        <v>77</v>
-      </c>
-      <c r="P9" s="5">
-        <f t="shared" ref="P9:X9" si="14">O9*0.9</f>
-        <v>69.3</v>
-      </c>
-      <c r="Q9" s="5">
-        <f t="shared" si="14"/>
-        <v>62.37</v>
-      </c>
-      <c r="R9" s="5">
-        <f t="shared" si="14"/>
-        <v>56.132999999999996</v>
-      </c>
-      <c r="S9" s="5">
-        <f t="shared" si="14"/>
-        <v>50.5197</v>
-      </c>
-      <c r="T9" s="5">
-        <f t="shared" si="14"/>
-        <v>45.467730000000003</v>
-      </c>
-      <c r="U9" s="5">
-        <f t="shared" si="14"/>
-        <v>40.920957000000001</v>
-      </c>
       <c r="V9" s="5">
-        <f t="shared" si="14"/>
-        <v>36.8288613</v>
+        <f>-91.1+86.1</f>
+        <v>-5</v>
       </c>
       <c r="W9" s="5">
-        <f t="shared" si="14"/>
-        <v>33.14597517</v>
+        <v>96</v>
       </c>
       <c r="X9" s="5">
-        <f t="shared" si="14"/>
-        <v>29.831377653000001</v>
+        <v>62</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>-190</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>-283</v>
+      </c>
+      <c r="AA9" s="11">
+        <f>SUM(Q9:R9)</f>
+        <v>-297.10000000000002</v>
+      </c>
+      <c r="AB9" s="5">
+        <f t="shared" ref="X9:AF9" si="40">AA9*0.9</f>
+        <v>-267.39000000000004</v>
+      </c>
+      <c r="AC9" s="5">
+        <f t="shared" si="40"/>
+        <v>-240.65100000000004</v>
+      </c>
+      <c r="AD9" s="5">
+        <f t="shared" si="40"/>
+        <v>-216.58590000000004</v>
+      </c>
+      <c r="AE9" s="5">
+        <f t="shared" si="40"/>
+        <v>-194.92731000000003</v>
+      </c>
+      <c r="AF9" s="5">
+        <f t="shared" si="40"/>
+        <v>-175.43457900000004</v>
+      </c>
+      <c r="AG9" s="5">
+        <f t="shared" ref="AG9" si="41">AF9*0.9</f>
+        <v>-157.89112110000005</v>
+      </c>
+      <c r="AH9" s="5">
+        <f t="shared" ref="AH9" si="42">AG9*0.9</f>
+        <v>-142.10200899000006</v>
+      </c>
+      <c r="AI9" s="5">
+        <f t="shared" ref="AI9" si="43">AH9*0.9</f>
+        <v>-127.89180809100006</v>
+      </c>
+      <c r="AJ9" s="5">
+        <f t="shared" ref="AJ9" si="44">AI9*0.9</f>
+        <v>-115.10262728190006</v>
+      </c>
+      <c r="AK9" s="5">
+        <f t="shared" ref="AK9" si="45">AJ9*0.9</f>
+        <v>-103.59236455371006</v>
       </c>
     </row>
-    <row r="10" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" ref="C10:J10" si="15">C8-C9</f>
+        <f t="shared" ref="C10:L10" si="46">C8-C9</f>
         <v>1031</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>1034.5000000000002</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>1127.5999999999999</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>1142.5999999999997</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>491.19999999999993</v>
       </c>
       <c r="H10" s="8">
-        <f t="shared" si="15"/>
-        <v>1485.1999999999998</v>
+        <f t="shared" si="46"/>
+        <v>1495.1999999999998</v>
       </c>
       <c r="I10" s="8">
-        <f t="shared" si="15"/>
-        <v>1058.5160000000005</v>
+        <f t="shared" ref="I10:J10" si="47">I8-I9</f>
+        <v>1674.8000000000006</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="15"/>
-        <v>1648.9669999999994</v>
+        <f t="shared" si="47"/>
+        <v>1760.1999999999994</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="46"/>
+        <v>2270</v>
       </c>
       <c r="L10" s="8">
-        <f>L8-L9</f>
+        <f t="shared" si="46"/>
+        <v>2365</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" ref="M10:N10" si="48">M8-M9</f>
+        <v>3022</v>
+      </c>
+      <c r="N10" s="8">
+        <f t="shared" si="48"/>
+        <v>2817</v>
+      </c>
+      <c r="O10" s="8">
+        <f t="shared" ref="O10:R10" si="49">O8-O9</f>
+        <v>3290</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" ref="P10" si="50">P8-P9</f>
+        <v>3141</v>
+      </c>
+      <c r="Q10" s="8">
+        <f t="shared" si="49"/>
+        <v>3475</v>
+      </c>
+      <c r="R10" s="8">
+        <f t="shared" si="49"/>
+        <v>3276.8119999999994</v>
+      </c>
+      <c r="T10" s="8">
+        <f>T8-T9</f>
         <v>2065.5</v>
       </c>
-      <c r="M10" s="8">
-        <f>M8-M9</f>
+      <c r="U10" s="8">
+        <f>U8-U9</f>
         <v>2270.2000000000003</v>
       </c>
-      <c r="N10" s="8">
-        <f>N8-N9</f>
-        <v>1976.3999999999994</v>
-      </c>
-      <c r="O10" s="8">
-        <f t="shared" ref="O10:X10" si="16">O8-O9</f>
-        <v>2707.4830000000002</v>
-      </c>
-      <c r="P10" s="8">
-        <f t="shared" si="16"/>
-        <v>3373.1047599999988</v>
-      </c>
-      <c r="Q10" s="8">
-        <f t="shared" si="16"/>
-        <v>3973.6673847999996</v>
-      </c>
-      <c r="R10" s="8">
-        <f t="shared" si="16"/>
-        <v>4464.388216792001</v>
-      </c>
-      <c r="S10" s="8">
-        <f t="shared" si="16"/>
-        <v>4827.3423495035204</v>
-      </c>
-      <c r="T10" s="8">
-        <f t="shared" si="16"/>
-        <v>5142.035550870457</v>
-      </c>
-      <c r="U10" s="8">
-        <f t="shared" si="16"/>
-        <v>5507.538347051749</v>
-      </c>
       <c r="V10" s="8">
-        <f t="shared" si="16"/>
-        <v>5802.6437991275034</v>
+        <f>V8-V9</f>
+        <v>1986.3999999999994</v>
       </c>
       <c r="W10" s="8">
-        <f t="shared" si="16"/>
-        <v>6016.7391070193062</v>
+        <f t="shared" ref="W10" si="51">W8-W9</f>
+        <v>3435</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" si="16"/>
-        <v>6237.4830637899431</v>
+        <f t="shared" ref="X10:Y10" si="52">X8-X9</f>
+        <v>4635</v>
+      </c>
+      <c r="Y10" s="8">
+        <f t="shared" si="52"/>
+        <v>5839</v>
+      </c>
+      <c r="Z10" s="8">
+        <f t="shared" ref="W10:AF10" si="53">Z8-Z9</f>
+        <v>6431</v>
+      </c>
+      <c r="AA10" s="8">
+        <f t="shared" si="53"/>
+        <v>6697.6119999999983</v>
+      </c>
+      <c r="AB10" s="8">
+        <f t="shared" si="53"/>
+        <v>7199.2765199999994</v>
+      </c>
+      <c r="AC10" s="8">
+        <f t="shared" si="53"/>
+        <v>7670.8959600000017</v>
+      </c>
+      <c r="AD10" s="8">
+        <f t="shared" si="53"/>
+        <v>8047.2402559200009</v>
+      </c>
+      <c r="AE10" s="8">
+        <f t="shared" si="53"/>
+        <v>8313.133091332802</v>
+      </c>
+      <c r="AF10" s="8">
+        <f t="shared" si="53"/>
+        <v>8590.8709644026894</v>
+      </c>
+      <c r="AG10" s="8">
+        <f t="shared" ref="AG10:AK10" si="54">AG8-AG9</f>
+        <v>8880.5487173072725</v>
+      </c>
+      <c r="AH10" s="8">
+        <f t="shared" si="54"/>
+        <v>9182.2926147108428</v>
+      </c>
+      <c r="AI10" s="8">
+        <f t="shared" si="54"/>
+        <v>9496.2584792433681</v>
+      </c>
+      <c r="AJ10" s="8">
+        <f t="shared" si="54"/>
+        <v>9822.6300527739349</v>
+      </c>
+      <c r="AK10" s="8">
+        <f t="shared" si="54"/>
+        <v>10161.617562099706</v>
       </c>
     </row>
-    <row r="11" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:165" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="5">
         <v>335</v>
       </c>
-      <c r="D11" s="9">
-        <f>L11-C11</f>
+      <c r="D11" s="5">
+        <f>T11-C11</f>
         <v>337.20000000000005</v>
       </c>
       <c r="E11" s="5">
         <v>383.4</v>
       </c>
-      <c r="F11" s="9">
-        <f>M11-E11</f>
+      <c r="F11" s="5">
+        <f>U11-E11</f>
         <v>367.6</v>
       </c>
       <c r="G11" s="5">
@@ -1503,65 +2038,107 @@
         <v>452.3</v>
       </c>
       <c r="I11" s="5">
-        <f>I10*0.33</f>
-        <v>349.3102800000002</v>
-      </c>
-      <c r="J11" s="5">
-        <f t="shared" ref="J11" si="17">J10*0.33</f>
-        <v>544.15910999999983</v>
-      </c>
-      <c r="L11" s="5">
+        <v>510.8</v>
+      </c>
+      <c r="J11" s="11">
+        <f t="shared" ref="J11:J12" si="55">W11-I11</f>
+        <v>504.2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>647</v>
+      </c>
+      <c r="L11" s="11">
+        <f t="shared" ref="L11:L12" si="56">X11-K11</f>
+        <v>658</v>
+      </c>
+      <c r="M11" s="5">
+        <v>831</v>
+      </c>
+      <c r="N11" s="11">
+        <f t="shared" ref="N11:N12" si="57">Y11-M11</f>
+        <v>792</v>
+      </c>
+      <c r="O11" s="5">
+        <v>927</v>
+      </c>
+      <c r="P11" s="11">
+        <f t="shared" ref="P11:P12" si="58">Z11-O11</f>
+        <v>918</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>1230</v>
+      </c>
+      <c r="R11" s="5">
+        <f>R10*0.28</f>
+        <v>917.50735999999995</v>
+      </c>
+      <c r="T11" s="5">
         <v>672.2</v>
       </c>
-      <c r="M11" s="5">
+      <c r="U11" s="5">
         <v>751</v>
       </c>
-      <c r="N11" s="9">
-        <f>SUM(G11:H11)</f>
+      <c r="V11" s="5">
         <v>613</v>
       </c>
-      <c r="O11" s="9">
-        <f>SUM(I11:J11)</f>
-        <v>893.46938999999998</v>
-      </c>
-      <c r="P11" s="5">
-        <f t="shared" ref="P11:X11" si="18">P10*0.33</f>
-        <v>1113.1245707999997</v>
-      </c>
-      <c r="Q11" s="5">
-        <f t="shared" si="18"/>
-        <v>1311.3102369839999</v>
-      </c>
-      <c r="R11" s="5">
-        <f t="shared" si="18"/>
-        <v>1473.2481115413605</v>
-      </c>
-      <c r="S11" s="5">
-        <f t="shared" si="18"/>
-        <v>1593.0229753361618</v>
-      </c>
-      <c r="T11" s="5">
-        <f t="shared" si="18"/>
-        <v>1696.8717317872508</v>
-      </c>
-      <c r="U11" s="5">
-        <f t="shared" si="18"/>
-        <v>1817.4876545270772</v>
-      </c>
-      <c r="V11" s="5">
-        <f t="shared" si="18"/>
-        <v>1914.8724537120761</v>
-      </c>
       <c r="W11" s="5">
-        <f t="shared" si="18"/>
-        <v>1985.5239053163712</v>
+        <v>1015</v>
       </c>
       <c r="X11" s="5">
-        <f t="shared" si="18"/>
-        <v>2058.3694110506813</v>
+        <v>1305</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>1623</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>1845</v>
+      </c>
+      <c r="AA11" s="11">
+        <f t="shared" ref="AA11:AA12" si="59">SUM(Q11:R11)</f>
+        <v>2147.5073600000001</v>
+      </c>
+      <c r="AB11" s="5">
+        <f>AB10*0.3</f>
+        <v>2159.7829559999996</v>
+      </c>
+      <c r="AC11" s="5">
+        <f t="shared" ref="AC11:AK11" si="60">AC10*0.3</f>
+        <v>2301.2687880000003</v>
+      </c>
+      <c r="AD11" s="5">
+        <f t="shared" si="60"/>
+        <v>2414.1720767760003</v>
+      </c>
+      <c r="AE11" s="5">
+        <f t="shared" si="60"/>
+        <v>2493.9399273998406</v>
+      </c>
+      <c r="AF11" s="5">
+        <f t="shared" si="60"/>
+        <v>2577.2612893208066</v>
+      </c>
+      <c r="AG11" s="5">
+        <f t="shared" si="60"/>
+        <v>2664.1646151921818</v>
+      </c>
+      <c r="AH11" s="5">
+        <f t="shared" si="60"/>
+        <v>2754.6877844132528</v>
+      </c>
+      <c r="AI11" s="5">
+        <f t="shared" si="60"/>
+        <v>2848.8775437730105</v>
+      </c>
+      <c r="AJ11" s="5">
+        <f t="shared" si="60"/>
+        <v>2946.7890158321802</v>
+      </c>
+      <c r="AK11" s="5">
+        <f t="shared" si="60"/>
+        <v>3048.4852686299114</v>
       </c>
     </row>
-    <row r="12" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:165" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>26</v>
       </c>
@@ -1569,16 +2146,16 @@
         <f>-12+2</f>
         <v>-10</v>
       </c>
-      <c r="D12" s="9">
-        <f>L12-C12</f>
+      <c r="D12" s="5">
+        <f>T12-C12</f>
         <v>-1.5000000000000018</v>
       </c>
       <c r="E12" s="5">
         <f>-12.8+2.7</f>
         <v>-10.100000000000001</v>
       </c>
-      <c r="F12" s="9">
-        <f>M12-E12</f>
+      <c r="F12" s="5">
+        <f>U12-E12</f>
         <v>1.2000000000000011</v>
       </c>
       <c r="G12" s="5">
@@ -1590,666 +2167,771 @@
         <v>-7.6000000000000014</v>
       </c>
       <c r="I12" s="5">
-        <v>-4</v>
-      </c>
-      <c r="J12" s="5">
-        <v>-11</v>
-      </c>
-      <c r="L12" s="5">
+        <f>-12.9+3.3</f>
+        <v>-9.6000000000000014</v>
+      </c>
+      <c r="J12" s="11">
+        <f t="shared" si="55"/>
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="K12" s="5">
+        <f>-25+6</f>
+        <v>-19</v>
+      </c>
+      <c r="L12" s="11">
+        <f t="shared" si="56"/>
+        <v>-18</v>
+      </c>
+      <c r="M12" s="5">
+        <f>-43+8</f>
+        <v>-35</v>
+      </c>
+      <c r="N12" s="11">
+        <f t="shared" si="57"/>
+        <v>-58</v>
+      </c>
+      <c r="O12" s="5">
+        <f>-16+10</f>
+        <v>-6</v>
+      </c>
+      <c r="P12" s="11">
+        <f t="shared" si="58"/>
+        <v>-10</v>
+      </c>
+      <c r="Q12" s="5">
+        <f>-26+25</f>
+        <v>-1</v>
+      </c>
+      <c r="R12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
         <f>-16.6+5.1</f>
         <v>-11.500000000000002</v>
       </c>
-      <c r="M12" s="5">
+      <c r="U12" s="5">
         <f>-15.9+7</f>
         <v>-8.9</v>
       </c>
-      <c r="N12" s="9">
-        <f>SUM(G12:H12)</f>
+      <c r="V12" s="5">
+        <f>-16.1+4.1</f>
         <v>-12.000000000000002</v>
       </c>
-      <c r="O12" s="9">
-        <f>SUM(I12:J12)</f>
-        <v>-15</v>
-      </c>
-      <c r="P12" s="5">
-        <f t="shared" ref="P12:X12" si="19">O12*1.02</f>
-        <v>-15.3</v>
-      </c>
-      <c r="Q12" s="5">
-        <f t="shared" si="19"/>
-        <v>-15.606000000000002</v>
-      </c>
-      <c r="R12" s="5">
-        <f t="shared" si="19"/>
-        <v>-15.918120000000002</v>
-      </c>
-      <c r="S12" s="5">
-        <f t="shared" si="19"/>
-        <v>-16.236482400000003</v>
-      </c>
-      <c r="T12" s="5">
-        <f t="shared" si="19"/>
-        <v>-16.561212048000005</v>
-      </c>
-      <c r="U12" s="5">
-        <f t="shared" si="19"/>
-        <v>-16.892436288960006</v>
-      </c>
-      <c r="V12" s="5">
-        <f t="shared" si="19"/>
-        <v>-17.230285014739206</v>
-      </c>
       <c r="W12" s="5">
-        <f t="shared" si="19"/>
-        <v>-17.574890715033991</v>
+        <f>-34+8</f>
+        <v>-26</v>
       </c>
       <c r="X12" s="5">
-        <f t="shared" si="19"/>
-        <v>-17.92638852933467</v>
+        <f>-50+13</f>
+        <v>-37</v>
+      </c>
+      <c r="Y12" s="5">
+        <f>-105+12</f>
+        <v>-93</v>
+      </c>
+      <c r="Z12" s="5">
+        <f>-44+28</f>
+        <v>-16</v>
+      </c>
+      <c r="AA12" s="11">
+        <f t="shared" si="59"/>
+        <v>-1</v>
+      </c>
+      <c r="AB12" s="5">
+        <f t="shared" ref="X12:AF12" si="61">AA12*1.02</f>
+        <v>-1.02</v>
+      </c>
+      <c r="AC12" s="5">
+        <f t="shared" si="61"/>
+        <v>-1.0404</v>
+      </c>
+      <c r="AD12" s="5">
+        <f t="shared" si="61"/>
+        <v>-1.0612079999999999</v>
+      </c>
+      <c r="AE12" s="5">
+        <f t="shared" si="61"/>
+        <v>-1.08243216</v>
+      </c>
+      <c r="AF12" s="5">
+        <f t="shared" si="61"/>
+        <v>-1.1040808032</v>
+      </c>
+      <c r="AG12" s="5">
+        <f t="shared" ref="AG12" si="62">AF12*1.02</f>
+        <v>-1.1261624192640001</v>
+      </c>
+      <c r="AH12" s="5">
+        <f t="shared" ref="AH12" si="63">AG12*1.02</f>
+        <v>-1.14868566764928</v>
+      </c>
+      <c r="AI12" s="5">
+        <f t="shared" ref="AI12" si="64">AH12*1.02</f>
+        <v>-1.1716593810022657</v>
+      </c>
+      <c r="AJ12" s="5">
+        <f t="shared" ref="AJ12" si="65">AI12*1.02</f>
+        <v>-1.1950925686223111</v>
+      </c>
+      <c r="AK12" s="5">
+        <f t="shared" ref="AK12" si="66">AJ12*1.02</f>
+        <v>-1.2189944199947573</v>
       </c>
     </row>
-    <row r="13" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:H13" si="20">C10-C11-C12</f>
+        <f t="shared" ref="C13:I13" si="67">C10-C11-C12</f>
         <v>706</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="67"/>
         <v>698.80000000000018</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="67"/>
         <v>754.3</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="67"/>
         <v>773.79999999999961</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="67"/>
         <v>334.89999999999992</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="20"/>
-        <v>1040.4999999999998</v>
+        <f t="shared" si="67"/>
+        <v>1050.4999999999998</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" ref="I13:J13" si="21">I10-I11-I12</f>
-        <v>713.20572000000038</v>
+        <f t="shared" si="67"/>
+        <v>1173.6000000000006</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="21"/>
-        <v>1115.8078899999996</v>
+        <f t="shared" ref="J13" si="68">J10-J11-J12</f>
+        <v>1272.3999999999994</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" ref="I13:L13" si="69">K10-K11-K12</f>
+        <v>1642</v>
       </c>
       <c r="L13" s="8">
-        <f>L10-L11-L12</f>
+        <f t="shared" si="69"/>
+        <v>1725</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" ref="M13:N13" si="70">M10-M11-M12</f>
+        <v>2226</v>
+      </c>
+      <c r="N13" s="8">
+        <f t="shared" si="70"/>
+        <v>2083</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" ref="O13:Q13" si="71">O10-O11-O12</f>
+        <v>2369</v>
+      </c>
+      <c r="P13" s="8">
+        <f t="shared" ref="P13" si="72">P10-P11-P12</f>
+        <v>2233</v>
+      </c>
+      <c r="Q13" s="8">
+        <f t="shared" si="71"/>
+        <v>2246</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" ref="R13" si="73">R10-R11-R12</f>
+        <v>2359.3046399999994</v>
+      </c>
+      <c r="T13" s="8">
+        <f>T10-T11-T12</f>
         <v>1404.8</v>
       </c>
-      <c r="M13" s="8">
-        <f>M10-M11-M12</f>
+      <c r="U13" s="8">
+        <f>U10-U11-U12</f>
         <v>1528.1000000000004</v>
       </c>
-      <c r="N13" s="8">
-        <f>N10-N11-N12</f>
-        <v>1375.3999999999994</v>
-      </c>
-      <c r="O13" s="8">
-        <f>O10-O11-O12</f>
-        <v>1829.0136100000002</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" ref="P13:X13" si="22">P10-P11-P12</f>
-        <v>2275.2801891999993</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" si="22"/>
-        <v>2677.9631478159999</v>
-      </c>
-      <c r="R13" s="8">
-        <f t="shared" si="22"/>
-        <v>3007.0582252506406</v>
-      </c>
-      <c r="S13" s="8">
-        <f t="shared" si="22"/>
-        <v>3250.5558565673587</v>
-      </c>
-      <c r="T13" s="8">
-        <f t="shared" si="22"/>
-        <v>3461.7250311312064</v>
-      </c>
-      <c r="U13" s="8">
-        <f t="shared" si="22"/>
-        <v>3706.943128813632</v>
-      </c>
       <c r="V13" s="8">
-        <f t="shared" si="22"/>
-        <v>3905.0016304301666</v>
+        <f>V10-V11-V12</f>
+        <v>1385.3999999999994</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" si="22"/>
-        <v>4048.7900924179689</v>
+        <f t="shared" ref="W13" si="74">W10-W11-W12</f>
+        <v>2446</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="22"/>
-        <v>4197.0400412685967</v>
-      </c>
-      <c r="Y13" s="1">
-        <f>X13*(1+$AA$19)</f>
-        <v>4155.0696408559106</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ref="Z13:CK13" si="23">Y13*(1+$AA$19)</f>
-        <v>4113.5189444473517</v>
-      </c>
-      <c r="AA13" s="1">
-        <f t="shared" si="23"/>
-        <v>4072.3837550028779</v>
-      </c>
-      <c r="AB13" s="1">
-        <f t="shared" si="23"/>
-        <v>4031.6599174528492</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" si="23"/>
-        <v>3991.3433182783206</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" si="23"/>
-        <v>3951.4298850955374</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" si="23"/>
-        <v>3911.9155862445818</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" si="23"/>
-        <v>3872.7964303821359</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" si="23"/>
-        <v>3834.0684660783145</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" si="23"/>
-        <v>3795.7277814175313</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" si="23"/>
-        <v>3757.7705036033558</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" si="23"/>
-        <v>3720.1927985673224</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" si="23"/>
-        <v>3682.9908705816492</v>
+        <f t="shared" ref="X13:Y13" si="75">X10-X11-X12</f>
+        <v>3367</v>
+      </c>
+      <c r="Y13" s="8">
+        <f t="shared" si="75"/>
+        <v>4309</v>
+      </c>
+      <c r="Z13" s="8">
+        <f t="shared" ref="X13:AF13" si="76">Z10-Z11-Z12</f>
+        <v>4602</v>
+      </c>
+      <c r="AA13" s="8">
+        <f t="shared" si="76"/>
+        <v>4551.1046399999977</v>
+      </c>
+      <c r="AB13" s="8">
+        <f t="shared" si="76"/>
+        <v>5040.5135640000008</v>
+      </c>
+      <c r="AC13" s="8">
+        <f t="shared" si="76"/>
+        <v>5370.6675720000012</v>
+      </c>
+      <c r="AD13" s="8">
+        <f t="shared" si="76"/>
+        <v>5634.1293871440002</v>
+      </c>
+      <c r="AE13" s="8">
+        <f t="shared" si="76"/>
+        <v>5820.2755960929617</v>
+      </c>
+      <c r="AF13" s="8">
+        <f t="shared" si="76"/>
+        <v>6014.7137558850836</v>
+      </c>
+      <c r="AG13" s="8">
+        <f t="shared" ref="AG13:AK13" si="77">AG10-AG11-AG12</f>
+        <v>6217.510264534355</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="77"/>
+        <v>6428.7535159652398</v>
+      </c>
+      <c r="AI13" s="8">
+        <f t="shared" si="77"/>
+        <v>6648.5525948513596</v>
+      </c>
+      <c r="AJ13" s="8">
+        <f t="shared" si="77"/>
+        <v>6877.0361295103767</v>
+      </c>
+      <c r="AK13" s="8">
+        <f t="shared" si="77"/>
+        <v>7114.3512878897891</v>
       </c>
       <c r="AL13" s="1">
-        <f t="shared" si="23"/>
-        <v>3646.1609618758325</v>
+        <f>AK13*(1+$AN$19)</f>
+        <v>7043.2077750108911</v>
       </c>
       <c r="AM13" s="1">
-        <f t="shared" si="23"/>
-        <v>3609.6993522570742</v>
+        <f t="shared" ref="AM13:CX13" si="78">AL13*(1+$AN$19)</f>
+        <v>6972.7756972607822</v>
       </c>
       <c r="AN13" s="1">
-        <f t="shared" si="23"/>
-        <v>3573.6023587345035</v>
+        <f t="shared" si="78"/>
+        <v>6903.0479402881747</v>
       </c>
       <c r="AO13" s="1">
-        <f t="shared" si="23"/>
-        <v>3537.8663351471582</v>
+        <f t="shared" si="78"/>
+        <v>6834.0174608852931</v>
       </c>
       <c r="AP13" s="1">
-        <f t="shared" si="23"/>
-        <v>3502.4876717956868</v>
+        <f t="shared" si="78"/>
+        <v>6765.6772862764401</v>
       </c>
       <c r="AQ13" s="1">
-        <f t="shared" si="23"/>
-        <v>3467.4627950777299</v>
+        <f t="shared" si="78"/>
+        <v>6698.0205134136759</v>
       </c>
       <c r="AR13" s="1">
-        <f t="shared" si="23"/>
-        <v>3432.7881671269524</v>
+        <f t="shared" si="78"/>
+        <v>6631.0403082795392</v>
       </c>
       <c r="AS13" s="1">
-        <f t="shared" si="23"/>
-        <v>3398.4602854556829</v>
+        <f t="shared" si="78"/>
+        <v>6564.7299051967439</v>
       </c>
       <c r="AT13" s="1">
-        <f t="shared" si="23"/>
-        <v>3364.4756826011262</v>
+        <f t="shared" si="78"/>
+        <v>6499.082606144776</v>
       </c>
       <c r="AU13" s="1">
-        <f t="shared" si="23"/>
-        <v>3330.8309257751148</v>
+        <f t="shared" si="78"/>
+        <v>6434.0917800833286</v>
       </c>
       <c r="AV13" s="1">
-        <f t="shared" si="23"/>
-        <v>3297.5226165173635</v>
+        <f t="shared" si="78"/>
+        <v>6369.7508622824953</v>
       </c>
       <c r="AW13" s="1">
-        <f t="shared" si="23"/>
-        <v>3264.5473903521897</v>
+        <f t="shared" si="78"/>
+        <v>6306.0533536596704</v>
       </c>
       <c r="AX13" s="1">
-        <f t="shared" si="23"/>
-        <v>3231.9019164486676</v>
+        <f t="shared" si="78"/>
+        <v>6242.9928201230732</v>
       </c>
       <c r="AY13" s="1">
-        <f t="shared" si="23"/>
-        <v>3199.5828972841809</v>
+        <f t="shared" si="78"/>
+        <v>6180.5628919218425</v>
       </c>
       <c r="AZ13" s="1">
-        <f t="shared" si="23"/>
-        <v>3167.587068311339</v>
+        <f t="shared" si="78"/>
+        <v>6118.7572630026243</v>
       </c>
       <c r="BA13" s="1">
-        <f t="shared" si="23"/>
-        <v>3135.9111976282256</v>
+        <f t="shared" si="78"/>
+        <v>6057.5696903725984</v>
       </c>
       <c r="BB13" s="1">
-        <f t="shared" si="23"/>
-        <v>3104.5520856519433</v>
+        <f t="shared" si="78"/>
+        <v>5996.9939934688728</v>
       </c>
       <c r="BC13" s="1">
-        <f t="shared" si="23"/>
-        <v>3073.5065647954239</v>
+        <f t="shared" si="78"/>
+        <v>5937.0240535341836</v>
       </c>
       <c r="BD13" s="1">
-        <f t="shared" si="23"/>
-        <v>3042.7714991474695</v>
+        <f t="shared" si="78"/>
+        <v>5877.6538129988421</v>
       </c>
       <c r="BE13" s="1">
-        <f t="shared" si="23"/>
-        <v>3012.3437841559949</v>
+        <f t="shared" si="78"/>
+        <v>5818.8772748688534</v>
       </c>
       <c r="BF13" s="1">
-        <f t="shared" si="23"/>
-        <v>2982.2203463144347</v>
+        <f t="shared" si="78"/>
+        <v>5760.6885021201651</v>
       </c>
       <c r="BG13" s="1">
-        <f t="shared" si="23"/>
-        <v>2952.3981428512902</v>
+        <f t="shared" si="78"/>
+        <v>5703.0816170989638</v>
       </c>
       <c r="BH13" s="1">
-        <f t="shared" si="23"/>
-        <v>2922.8741614227774</v>
+        <f t="shared" si="78"/>
+        <v>5646.0508009279738</v>
       </c>
       <c r="BI13" s="1">
-        <f t="shared" si="23"/>
-        <v>2893.6454198085498</v>
+        <f t="shared" si="78"/>
+        <v>5589.5902929186941</v>
       </c>
       <c r="BJ13" s="1">
-        <f t="shared" si="23"/>
-        <v>2864.7089656104645</v>
+        <f t="shared" si="78"/>
+        <v>5533.6943899895068</v>
       </c>
       <c r="BK13" s="1">
-        <f t="shared" si="23"/>
-        <v>2836.0618759543599</v>
+        <f t="shared" si="78"/>
+        <v>5478.3574460896116</v>
       </c>
       <c r="BL13" s="1">
-        <f t="shared" si="23"/>
-        <v>2807.7012571948162</v>
+        <f t="shared" si="78"/>
+        <v>5423.5738716287151</v>
       </c>
       <c r="BM13" s="1">
-        <f t="shared" si="23"/>
-        <v>2779.624244622868</v>
+        <f t="shared" si="78"/>
+        <v>5369.3381329124277</v>
       </c>
       <c r="BN13" s="1">
-        <f t="shared" si="23"/>
-        <v>2751.8280021766391</v>
+        <f t="shared" si="78"/>
+        <v>5315.6447515833033</v>
       </c>
       <c r="BO13" s="1">
-        <f t="shared" si="23"/>
-        <v>2724.3097221548728</v>
+        <f t="shared" si="78"/>
+        <v>5262.4883040674704</v>
       </c>
       <c r="BP13" s="1">
-        <f t="shared" si="23"/>
-        <v>2697.066624933324</v>
+        <f t="shared" si="78"/>
+        <v>5209.8634210267955</v>
       </c>
       <c r="BQ13" s="1">
-        <f t="shared" si="23"/>
-        <v>2670.0959586839908</v>
+        <f t="shared" si="78"/>
+        <v>5157.7647868165277</v>
       </c>
       <c r="BR13" s="1">
-        <f t="shared" si="23"/>
-        <v>2643.394999097151</v>
+        <f t="shared" si="78"/>
+        <v>5106.1871389483622</v>
       </c>
       <c r="BS13" s="1">
-        <f t="shared" si="23"/>
-        <v>2616.9610491061794</v>
+        <f t="shared" si="78"/>
+        <v>5055.1252675588785</v>
       </c>
       <c r="BT13" s="1">
-        <f t="shared" si="23"/>
-        <v>2590.7914386151174</v>
+        <f t="shared" si="78"/>
+        <v>5004.5740148832892</v>
       </c>
       <c r="BU13" s="1">
-        <f t="shared" si="23"/>
-        <v>2564.8835242289661</v>
+        <f t="shared" si="78"/>
+        <v>4954.5282747344563</v>
       </c>
       <c r="BV13" s="1">
-        <f t="shared" si="23"/>
-        <v>2539.2346889866762</v>
+        <f t="shared" si="78"/>
+        <v>4904.9829919871117</v>
       </c>
       <c r="BW13" s="1">
-        <f t="shared" si="23"/>
-        <v>2513.8423420968093</v>
+        <f t="shared" si="78"/>
+        <v>4855.933162067241</v>
       </c>
       <c r="BX13" s="1">
-        <f t="shared" si="23"/>
-        <v>2488.7039186758411</v>
+        <f t="shared" si="78"/>
+        <v>4807.3738304465687</v>
       </c>
       <c r="BY13" s="1">
-        <f t="shared" si="23"/>
-        <v>2463.8168794890826</v>
+        <f t="shared" si="78"/>
+        <v>4759.3000921421026</v>
       </c>
       <c r="BZ13" s="1">
-        <f t="shared" si="23"/>
-        <v>2439.1787106941915</v>
+        <f t="shared" si="78"/>
+        <v>4711.7070912206818</v>
       </c>
       <c r="CA13" s="1">
-        <f t="shared" si="23"/>
-        <v>2414.7869235872495</v>
+        <f t="shared" si="78"/>
+        <v>4664.5900203084748</v>
       </c>
       <c r="CB13" s="1">
-        <f t="shared" si="23"/>
-        <v>2390.6390543513771</v>
+        <f t="shared" si="78"/>
+        <v>4617.9441201053896</v>
       </c>
       <c r="CC13" s="1">
-        <f t="shared" si="23"/>
-        <v>2366.7326638078634</v>
+        <f t="shared" si="78"/>
+        <v>4571.7646789043356</v>
       </c>
       <c r="CD13" s="1">
-        <f t="shared" si="23"/>
-        <v>2343.0653371697849</v>
+        <f t="shared" si="78"/>
+        <v>4526.0470321152925</v>
       </c>
       <c r="CE13" s="1">
-        <f t="shared" si="23"/>
-        <v>2319.6346837980873</v>
+        <f t="shared" si="78"/>
+        <v>4480.7865617941397</v>
       </c>
       <c r="CF13" s="1">
-        <f t="shared" si="23"/>
-        <v>2296.4383369601064</v>
+        <f t="shared" si="78"/>
+        <v>4435.9786961761984</v>
       </c>
       <c r="CG13" s="1">
-        <f t="shared" si="23"/>
-        <v>2273.4739535905055</v>
+        <f t="shared" si="78"/>
+        <v>4391.6189092144359</v>
       </c>
       <c r="CH13" s="1">
-        <f t="shared" si="23"/>
-        <v>2250.7392140546003</v>
+        <f t="shared" si="78"/>
+        <v>4347.7027201222918</v>
       </c>
       <c r="CI13" s="1">
-        <f t="shared" si="23"/>
-        <v>2228.2318219140543</v>
+        <f t="shared" si="78"/>
+        <v>4304.2256929210689</v>
       </c>
       <c r="CJ13" s="1">
-        <f t="shared" si="23"/>
-        <v>2205.9495036949138</v>
+        <f t="shared" si="78"/>
+        <v>4261.1834359918585</v>
       </c>
       <c r="CK13" s="1">
-        <f t="shared" si="23"/>
-        <v>2183.8900086579647</v>
+        <f t="shared" si="78"/>
+        <v>4218.5716016319402</v>
       </c>
       <c r="CL13" s="1">
-        <f t="shared" ref="CL13:EV13" si="24">CK13*(1+$AA$19)</f>
-        <v>2162.0511085713852</v>
+        <f t="shared" si="78"/>
+        <v>4176.3858856156212</v>
       </c>
       <c r="CM13" s="1">
-        <f t="shared" si="24"/>
-        <v>2140.4305974856711</v>
+        <f t="shared" si="78"/>
+        <v>4134.6220267594654</v>
       </c>
       <c r="CN13" s="1">
-        <f t="shared" si="24"/>
-        <v>2119.0262915108142</v>
+        <f t="shared" si="78"/>
+        <v>4093.2758064918708</v>
       </c>
       <c r="CO13" s="1">
-        <f t="shared" si="24"/>
-        <v>2097.836028595706</v>
+        <f t="shared" si="78"/>
+        <v>4052.343048426952</v>
       </c>
       <c r="CP13" s="1">
-        <f t="shared" si="24"/>
-        <v>2076.857668309749</v>
+        <f t="shared" si="78"/>
+        <v>4011.8196179426823</v>
       </c>
       <c r="CQ13" s="1">
-        <f t="shared" si="24"/>
-        <v>2056.0890916266517</v>
+        <f t="shared" si="78"/>
+        <v>3971.7014217632554</v>
       </c>
       <c r="CR13" s="1">
-        <f t="shared" si="24"/>
-        <v>2035.5282007103851</v>
+        <f t="shared" si="78"/>
+        <v>3931.9844075456231</v>
       </c>
       <c r="CS13" s="1">
-        <f t="shared" si="24"/>
-        <v>2015.1729187032813</v>
+        <f t="shared" si="78"/>
+        <v>3892.6645634701667</v>
       </c>
       <c r="CT13" s="1">
-        <f t="shared" si="24"/>
-        <v>1995.0211895162486</v>
+        <f t="shared" si="78"/>
+        <v>3853.7379178354649</v>
       </c>
       <c r="CU13" s="1">
-        <f t="shared" si="24"/>
-        <v>1975.0709776210861</v>
+        <f t="shared" si="78"/>
+        <v>3815.2005386571104</v>
       </c>
       <c r="CV13" s="1">
-        <f t="shared" si="24"/>
-        <v>1955.3202678448752</v>
+        <f t="shared" si="78"/>
+        <v>3777.0485332705393</v>
       </c>
       <c r="CW13" s="1">
-        <f t="shared" si="24"/>
-        <v>1935.7670651664264</v>
+        <f t="shared" si="78"/>
+        <v>3739.2780479378339</v>
       </c>
       <c r="CX13" s="1">
-        <f t="shared" si="24"/>
-        <v>1916.4093945147622</v>
+        <f t="shared" si="78"/>
+        <v>3701.8852674584555</v>
       </c>
       <c r="CY13" s="1">
-        <f t="shared" si="24"/>
-        <v>1897.2453005696145</v>
+        <f t="shared" ref="CY13:FI13" si="79">CX13*(1+$AN$19)</f>
+        <v>3664.8664147838708</v>
       </c>
       <c r="CZ13" s="1">
-        <f t="shared" si="24"/>
-        <v>1878.2728475639183</v>
+        <f t="shared" si="79"/>
+        <v>3628.2177506360322</v>
       </c>
       <c r="DA13" s="1">
-        <f t="shared" si="24"/>
-        <v>1859.490119088279</v>
+        <f t="shared" si="79"/>
+        <v>3591.9355731296719</v>
       </c>
       <c r="DB13" s="1">
-        <f t="shared" si="24"/>
-        <v>1840.8952178973962</v>
+        <f t="shared" si="79"/>
+        <v>3556.0162173983749</v>
       </c>
       <c r="DC13" s="1">
-        <f t="shared" si="24"/>
-        <v>1822.4862657184221</v>
+        <f t="shared" si="79"/>
+        <v>3520.4560552243911</v>
       </c>
       <c r="DD13" s="1">
-        <f t="shared" si="24"/>
-        <v>1804.2614030612378</v>
+        <f t="shared" si="79"/>
+        <v>3485.2514946721471</v>
       </c>
       <c r="DE13" s="1">
-        <f t="shared" si="24"/>
-        <v>1786.2187890306254</v>
+        <f t="shared" si="79"/>
+        <v>3450.3989797254258</v>
       </c>
       <c r="DF13" s="1">
-        <f t="shared" si="24"/>
-        <v>1768.3566011403191</v>
+        <f t="shared" si="79"/>
+        <v>3415.8949899281715</v>
       </c>
       <c r="DG13" s="1">
-        <f t="shared" si="24"/>
-        <v>1750.6730351289159</v>
+        <f t="shared" si="79"/>
+        <v>3381.7360400288899</v>
       </c>
       <c r="DH13" s="1">
-        <f t="shared" si="24"/>
-        <v>1733.1663047776267</v>
+        <f t="shared" si="79"/>
+        <v>3347.9186796286008</v>
       </c>
       <c r="DI13" s="1">
-        <f t="shared" si="24"/>
-        <v>1715.8346417298503</v>
+        <f t="shared" si="79"/>
+        <v>3314.439492832315</v>
       </c>
       <c r="DJ13" s="1">
-        <f t="shared" si="24"/>
-        <v>1698.6762953125517</v>
+        <f t="shared" si="79"/>
+        <v>3281.295097903992</v>
       </c>
       <c r="DK13" s="1">
-        <f t="shared" si="24"/>
-        <v>1681.6895323594263</v>
+        <f t="shared" si="79"/>
+        <v>3248.4821469249518</v>
       </c>
       <c r="DL13" s="1">
-        <f t="shared" si="24"/>
-        <v>1664.872637035832</v>
+        <f t="shared" si="79"/>
+        <v>3215.9973254557021</v>
       </c>
       <c r="DM13" s="1">
-        <f t="shared" si="24"/>
-        <v>1648.2239106654736</v>
+        <f t="shared" si="79"/>
+        <v>3183.8373522011452</v>
       </c>
       <c r="DN13" s="1">
-        <f t="shared" si="24"/>
-        <v>1631.7416715588188</v>
+        <f t="shared" si="79"/>
+        <v>3151.9989786791339</v>
       </c>
       <c r="DO13" s="1">
-        <f t="shared" si="24"/>
-        <v>1615.4242548432305</v>
+        <f t="shared" si="79"/>
+        <v>3120.4789888923424</v>
       </c>
       <c r="DP13" s="1">
-        <f t="shared" si="24"/>
-        <v>1599.2700122947981</v>
+        <f t="shared" si="79"/>
+        <v>3089.2741990034187</v>
       </c>
       <c r="DQ13" s="1">
-        <f t="shared" si="24"/>
-        <v>1583.2773121718501</v>
+        <f t="shared" si="79"/>
+        <v>3058.3814570133845</v>
       </c>
       <c r="DR13" s="1">
-        <f t="shared" si="24"/>
-        <v>1567.4445390501317</v>
+        <f t="shared" si="79"/>
+        <v>3027.7976424432509</v>
       </c>
       <c r="DS13" s="1">
-        <f t="shared" si="24"/>
-        <v>1551.7700936596302</v>
+        <f t="shared" si="79"/>
+        <v>2997.5196660188185</v>
       </c>
       <c r="DT13" s="1">
-        <f t="shared" si="24"/>
-        <v>1536.2523927230338</v>
+        <f t="shared" si="79"/>
+        <v>2967.5444693586301</v>
       </c>
       <c r="DU13" s="1">
-        <f t="shared" si="24"/>
-        <v>1520.8898687958035</v>
+        <f t="shared" si="79"/>
+        <v>2937.8690246650435</v>
       </c>
       <c r="DV13" s="1">
-        <f t="shared" si="24"/>
-        <v>1505.6809701078455</v>
+        <f t="shared" si="79"/>
+        <v>2908.4903344183931</v>
       </c>
       <c r="DW13" s="1">
-        <f t="shared" si="24"/>
-        <v>1490.624160406767</v>
+        <f t="shared" si="79"/>
+        <v>2879.405431074209</v>
       </c>
       <c r="DX13" s="1">
-        <f t="shared" si="24"/>
-        <v>1475.7179188026994</v>
+        <f t="shared" si="79"/>
+        <v>2850.611376763467</v>
       </c>
       <c r="DY13" s="1">
-        <f t="shared" si="24"/>
-        <v>1460.9607396146723</v>
+        <f t="shared" si="79"/>
+        <v>2822.1052629958322</v>
       </c>
       <c r="DZ13" s="1">
-        <f t="shared" si="24"/>
-        <v>1446.3511322185257</v>
+        <f t="shared" si="79"/>
+        <v>2793.884210365874</v>
       </c>
       <c r="EA13" s="1">
-        <f t="shared" si="24"/>
-        <v>1431.8876208963404</v>
+        <f t="shared" si="79"/>
+        <v>2765.9453682622152</v>
       </c>
       <c r="EB13" s="1">
-        <f t="shared" si="24"/>
-        <v>1417.5687446873769</v>
+        <f t="shared" si="79"/>
+        <v>2738.2859145795928</v>
       </c>
       <c r="EC13" s="1">
-        <f t="shared" si="24"/>
-        <v>1403.3930572405031</v>
+        <f t="shared" si="79"/>
+        <v>2710.9030554337969</v>
       </c>
       <c r="ED13" s="1">
-        <f t="shared" si="24"/>
-        <v>1389.359126668098</v>
+        <f t="shared" si="79"/>
+        <v>2683.7940248794589</v>
       </c>
       <c r="EE13" s="1">
-        <f t="shared" si="24"/>
-        <v>1375.4655354014171</v>
+        <f t="shared" si="79"/>
+        <v>2656.9560846306645</v>
       </c>
       <c r="EF13" s="1">
-        <f t="shared" si="24"/>
-        <v>1361.710880047403</v>
+        <f t="shared" si="79"/>
+        <v>2630.3865237843579</v>
       </c>
       <c r="EG13" s="1">
-        <f t="shared" si="24"/>
-        <v>1348.093771246929</v>
+        <f t="shared" si="79"/>
+        <v>2604.0826585465143</v>
       </c>
       <c r="EH13" s="1">
-        <f t="shared" si="24"/>
-        <v>1334.6128335344597</v>
+        <f t="shared" si="79"/>
+        <v>2578.041831961049</v>
       </c>
       <c r="EI13" s="1">
-        <f t="shared" si="24"/>
-        <v>1321.266705199115</v>
+        <f t="shared" si="79"/>
+        <v>2552.2614136414386</v>
       </c>
       <c r="EJ13" s="1">
-        <f t="shared" si="24"/>
-        <v>1308.0540381471237</v>
+        <f t="shared" si="79"/>
+        <v>2526.738799505024</v>
       </c>
       <c r="EK13" s="1">
-        <f t="shared" si="24"/>
-        <v>1294.9734977656524</v>
+        <f t="shared" si="79"/>
+        <v>2501.4714115099737</v>
       </c>
       <c r="EL13" s="1">
-        <f t="shared" si="24"/>
-        <v>1282.0237627879958</v>
+        <f t="shared" si="79"/>
+        <v>2476.456697394874</v>
       </c>
       <c r="EM13" s="1">
-        <f t="shared" si="24"/>
-        <v>1269.2035251601158</v>
+        <f t="shared" si="79"/>
+        <v>2451.6921304209254</v>
       </c>
       <c r="EN13" s="1">
-        <f t="shared" si="24"/>
-        <v>1256.5114899085147</v>
+        <f t="shared" si="79"/>
+        <v>2427.1752091167164</v>
       </c>
       <c r="EO13" s="1">
-        <f t="shared" si="24"/>
-        <v>1243.9463750094296</v>
+        <f t="shared" si="79"/>
+        <v>2402.903457025549</v>
       </c>
       <c r="EP13" s="1">
-        <f t="shared" si="24"/>
-        <v>1231.5069112593353</v>
+        <f t="shared" si="79"/>
+        <v>2378.8744224552934</v>
       </c>
       <c r="EQ13" s="1">
-        <f t="shared" si="24"/>
-        <v>1219.1918421467419</v>
+        <f t="shared" si="79"/>
+        <v>2355.0856782307405</v>
       </c>
       <c r="ER13" s="1">
-        <f t="shared" si="24"/>
-        <v>1206.9999237252746</v>
+        <f t="shared" si="79"/>
+        <v>2331.5348214484329</v>
       </c>
       <c r="ES13" s="1">
-        <f t="shared" si="24"/>
-        <v>1194.9299244880219</v>
+        <f t="shared" si="79"/>
+        <v>2308.2194732339485</v>
       </c>
       <c r="ET13" s="1">
-        <f t="shared" si="24"/>
-        <v>1182.9806252431417</v>
+        <f t="shared" si="79"/>
+        <v>2285.1372785016092</v>
       </c>
       <c r="EU13" s="1">
-        <f t="shared" si="24"/>
-        <v>1171.1508189907104</v>
+        <f t="shared" si="79"/>
+        <v>2262.2859057165929</v>
       </c>
       <c r="EV13" s="1">
-        <f t="shared" si="24"/>
-        <v>1159.4393108008032</v>
+        <f t="shared" si="79"/>
+        <v>2239.663046659427</v>
+      </c>
+      <c r="EW13" s="1">
+        <f t="shared" si="79"/>
+        <v>2217.2664161928328</v>
+      </c>
+      <c r="EX13" s="1">
+        <f t="shared" si="79"/>
+        <v>2195.0937520309044</v>
+      </c>
+      <c r="EY13" s="1">
+        <f t="shared" si="79"/>
+        <v>2173.1428145105951</v>
+      </c>
+      <c r="EZ13" s="1">
+        <f t="shared" si="79"/>
+        <v>2151.4113863654893</v>
+      </c>
+      <c r="FA13" s="1">
+        <f t="shared" si="79"/>
+        <v>2129.8972725018343</v>
+      </c>
+      <c r="FB13" s="1">
+        <f t="shared" si="79"/>
+        <v>2108.598299776816</v>
+      </c>
+      <c r="FC13" s="1">
+        <f t="shared" si="79"/>
+        <v>2087.512316779048</v>
+      </c>
+      <c r="FD13" s="1">
+        <f t="shared" si="79"/>
+        <v>2066.6371936112573</v>
+      </c>
+      <c r="FE13" s="1">
+        <f t="shared" si="79"/>
+        <v>2045.9708216751446</v>
+      </c>
+      <c r="FF13" s="1">
+        <f t="shared" si="79"/>
+        <v>2025.5111134583931</v>
+      </c>
+      <c r="FG13" s="1">
+        <f t="shared" si="79"/>
+        <v>2005.2560023238091</v>
+      </c>
+      <c r="FH13" s="1">
+        <f t="shared" si="79"/>
+        <v>1985.2034423005709</v>
+      </c>
+      <c r="FI13" s="1">
+        <f t="shared" si="79"/>
+        <v>1965.3514078775652</v>
       </c>
     </row>
-    <row r="14" spans="2:152" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:165" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>2</v>
       </c>
@@ -2277,6 +2959,9 @@
       <c r="J14" s="5">
         <v>105.569</v>
       </c>
+      <c r="K14" s="5">
+        <v>105.569</v>
+      </c>
       <c r="L14" s="5">
         <v>105.569</v>
       </c>
@@ -2298,9 +2983,6 @@
       <c r="R14" s="5">
         <v>105.569</v>
       </c>
-      <c r="S14" s="5">
-        <v>105.569</v>
-      </c>
       <c r="T14" s="5">
         <v>105.569</v>
       </c>
@@ -2316,662 +2998,1204 @@
       <c r="X14" s="5">
         <v>105.569</v>
       </c>
+      <c r="Y14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AA14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AE14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AF14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AG14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AH14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AI14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AJ14" s="5">
+        <v>105.569</v>
+      </c>
+      <c r="AK14" s="5">
+        <v>105.569</v>
+      </c>
     </row>
-    <row r="15" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:H15" si="25">C13/C14</f>
+        <f t="shared" ref="C15:I15" si="80">C13/C14</f>
         <v>6.6875692674932985</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="80"/>
         <v>6.6193674279381272</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="80"/>
         <v>7.1450899411759128</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="80"/>
         <v>7.3298032566378346</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="80"/>
         <v>3.1723327870871176</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="25"/>
-        <v>9.8561130634940159</v>
+        <f t="shared" si="80"/>
+        <v>9.9508378406539766</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" ref="I15:J15" si="26">I13/I14</f>
-        <v>6.7558252896210096</v>
+        <f t="shared" si="80"/>
+        <v>11.116899847493114</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="26"/>
-        <v>10.569465373357705</v>
+        <f t="shared" ref="J15" si="81">J13/J14</f>
+        <v>12.052780645833526</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" ref="I15:L15" si="82">K13/K14</f>
+        <v>15.553808409665717</v>
       </c>
       <c r="L15" s="7">
-        <f>L13/L14</f>
+        <f t="shared" si="82"/>
+        <v>16.340024060093398</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" ref="M15:N15" si="83">M13/M14</f>
+        <v>21.085735395807482</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="83"/>
+        <v>19.73117108242003</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" ref="O15:Q15" si="84">O13/O14</f>
+        <v>22.440299709194935</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" ref="P15" si="85">P13/P14</f>
+        <v>21.152042739819453</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="84"/>
+        <v>21.275184950127404</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" ref="R15" si="86">R13/R14</f>
+        <v>22.348460627646368</v>
+      </c>
+      <c r="T15" s="7">
+        <f>T13/T14</f>
         <v>13.306936695431423</v>
       </c>
-      <c r="M15" s="7">
-        <f>M13/M14</f>
+      <c r="U15" s="7">
+        <f>U13/U14</f>
         <v>14.474893197813754</v>
       </c>
-      <c r="N15" s="7">
-        <f>N13/N14</f>
-        <v>13.02844585058113</v>
-      </c>
-      <c r="O15" s="7">
-        <f>O13/O14</f>
-        <v>17.325290662978716</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" ref="P15:X15" si="27">P13/P14</f>
-        <v>21.552540889844551</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" si="27"/>
-        <v>25.366946241946025</v>
-      </c>
-      <c r="R15" s="7">
-        <f t="shared" si="27"/>
-        <v>28.484292029389692</v>
-      </c>
-      <c r="S15" s="7">
-        <f t="shared" si="27"/>
-        <v>30.790817915935158</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" si="27"/>
-        <v>32.791113216296509</v>
-      </c>
-      <c r="U15" s="7">
-        <f t="shared" si="27"/>
-        <v>35.113936182152258</v>
-      </c>
       <c r="V15" s="7">
-        <f t="shared" si="27"/>
-        <v>36.990040925178477</v>
+        <f>V13/V14</f>
+        <v>13.123170627741093</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" si="27"/>
-        <v>38.352073927175297</v>
+        <f t="shared" ref="W15" si="87">W13/W14</f>
+        <v>23.169680493326638</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="27"/>
-        <v>39.756368264060441</v>
+        <f t="shared" ref="X15:Y15" si="88">X13/X14</f>
+        <v>31.893832469759115</v>
+      </c>
+      <c r="Y15" s="7">
+        <f t="shared" si="88"/>
+        <v>40.816906478227509</v>
+      </c>
+      <c r="Z15" s="7">
+        <f t="shared" ref="X15:AF15" si="89">Z13/Z14</f>
+        <v>43.592342449014389</v>
+      </c>
+      <c r="AA15" s="7">
+        <f t="shared" si="89"/>
+        <v>43.110237285566761</v>
+      </c>
+      <c r="AB15" s="7">
+        <f t="shared" si="89"/>
+        <v>47.74615241216646</v>
+      </c>
+      <c r="AC15" s="7">
+        <f t="shared" si="89"/>
+        <v>50.873528895793285</v>
+      </c>
+      <c r="AD15" s="7">
+        <f t="shared" si="89"/>
+        <v>53.369165068760715</v>
+      </c>
+      <c r="AE15" s="7">
+        <f t="shared" si="89"/>
+        <v>55.13243088494692</v>
+      </c>
+      <c r="AF15" s="7">
+        <f t="shared" si="89"/>
+        <v>56.974242020717099</v>
+      </c>
+      <c r="AG15" s="7">
+        <f t="shared" ref="AG15:AK15" si="90">AG13/AG14</f>
+        <v>58.895227429779148</v>
+      </c>
+      <c r="AH15" s="7">
+        <f t="shared" si="90"/>
+        <v>60.896224421612779</v>
+      </c>
+      <c r="AI15" s="7">
+        <f t="shared" si="90"/>
+        <v>62.978266298358037</v>
+      </c>
+      <c r="AJ15" s="7">
+        <f t="shared" si="90"/>
+        <v>65.142571488887612</v>
+      </c>
+      <c r="AK15" s="7">
+        <f t="shared" si="90"/>
+        <v>67.390534038304693</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <f>E3/C3-1</f>
         <v>0.15113915177006643</v>
       </c>
-      <c r="F17" s="11">
-        <f t="shared" ref="F17:J17" si="28">F3/D3-1</f>
+      <c r="F17" s="9">
+        <f t="shared" ref="F17:J17" si="91">F3/D3-1</f>
         <v>0.15614660627670141</v>
       </c>
-      <c r="G17" s="11">
-        <f t="shared" si="28"/>
+      <c r="G17" s="9">
+        <f t="shared" si="91"/>
         <v>-0.24243346933804266</v>
       </c>
-      <c r="H17" s="11">
-        <f t="shared" si="28"/>
+      <c r="H17" s="9">
+        <f t="shared" si="91"/>
         <v>8.3963102911758014E-2</v>
       </c>
-      <c r="I17" s="11">
-        <f t="shared" si="28"/>
-        <v>0.32000000000000006</v>
-      </c>
-      <c r="J17" s="11">
-        <f t="shared" si="28"/>
-        <v>0.15000000000000013</v>
-      </c>
-      <c r="M17" s="11">
-        <f>M3/L3-1</f>
+      <c r="I17" s="9">
+        <f t="shared" si="91"/>
+        <v>0.70221061093247594</v>
+      </c>
+      <c r="J17" s="9">
+        <f t="shared" si="91"/>
+        <v>0.21671707592146405</v>
+      </c>
+      <c r="K17" s="9">
+        <f t="shared" ref="K17" si="92">K3/I3-1</f>
+        <v>0.29276758518098744</v>
+      </c>
+      <c r="L17" s="9">
+        <f t="shared" ref="L17" si="93">L3/J3-1</f>
+        <v>0.29073711264193491</v>
+      </c>
+      <c r="M17" s="9">
+        <f t="shared" ref="M17" si="94">M3/K3-1</f>
+        <v>0.22337899543378992</v>
+      </c>
+      <c r="N17" s="9">
+        <f t="shared" ref="N17" si="95">N3/L3-1</f>
+        <v>9.8253631467275948E-2</v>
+      </c>
+      <c r="O17" s="9">
+        <f t="shared" ref="O17" si="96">O3/M3-1</f>
+        <v>0.12033442818751872</v>
+      </c>
+      <c r="P17" s="9">
+        <f t="shared" ref="P17:Q17" si="97">P3/N3-1</f>
+        <v>0.13924803091098226</v>
+      </c>
+      <c r="Q17" s="9">
+        <f t="shared" si="97"/>
+        <v>7.0628997867803855E-2</v>
+      </c>
+      <c r="R17" s="9">
+        <f t="shared" ref="R17" si="98">R3/P3-1</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="U17" s="9">
+        <f>U3/T3-1</f>
         <v>0.15375203231591805</v>
       </c>
-      <c r="N17" s="11">
-        <f t="shared" ref="N17:X17" si="29">N3/M3-1</f>
+      <c r="V17" s="9">
+        <f t="shared" ref="V17:AF17" si="99">V3/U3-1</f>
         <v>-7.1766859400877459E-2</v>
       </c>
-      <c r="O17" s="11">
-        <f t="shared" si="29"/>
-        <v>0.21619713901148785</v>
-      </c>
-      <c r="P17" s="11">
-        <f t="shared" si="29"/>
-        <v>0.15999999999999992</v>
-      </c>
-      <c r="Q17" s="11">
-        <f t="shared" si="29"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="R17" s="11">
-        <f t="shared" si="29"/>
-        <v>9.000000000000008E-2</v>
-      </c>
-      <c r="S17" s="11">
-        <f t="shared" si="29"/>
+      <c r="W17" s="9">
+        <f t="shared" si="99"/>
+        <v>0.40576579960559678</v>
+      </c>
+      <c r="X17" s="9">
+        <f t="shared" si="99"/>
+        <v>0.2916945001113338</v>
+      </c>
+      <c r="Y17" s="9">
+        <f t="shared" si="99"/>
+        <v>0.15730046543699361</v>
+      </c>
+      <c r="Z17" s="9">
+        <f t="shared" si="99"/>
+        <v>0.12981306323080366</v>
+      </c>
+      <c r="AA17" s="9">
+        <f t="shared" si="99"/>
+        <v>6.5257745550428403E-2</v>
+      </c>
+      <c r="AB17" s="9">
+        <f t="shared" si="99"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="T17" s="11">
-        <f t="shared" si="29"/>
+      <c r="AC17" s="9">
+        <f t="shared" si="99"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="U17" s="11">
-        <f t="shared" si="29"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="V17" s="11">
-        <f t="shared" si="29"/>
+      <c r="AD17" s="9">
+        <f t="shared" si="99"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="W17" s="11">
-        <f t="shared" si="29"/>
+      <c r="AE17" s="9">
+        <f t="shared" si="99"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="X17" s="11">
-        <f t="shared" si="29"/>
+      <c r="AF17" s="9">
+        <f t="shared" si="99"/>
         <v>3.0000000000000027E-2</v>
       </c>
+      <c r="AG17" s="9">
+        <f t="shared" ref="AG17" si="100">AG3/AF3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH17" s="9">
+        <f t="shared" ref="AH17" si="101">AH3/AG3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AI17" s="9">
+        <f t="shared" ref="AI17" si="102">AI3/AH3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AJ17" s="9">
+        <f t="shared" ref="AJ17" si="103">AJ3/AI3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AK17" s="9">
+        <f t="shared" ref="AK17" si="104">AK3/AJ3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <f>C5/C3</f>
         <v>0.69891342446547489</v>
       </c>
-      <c r="D18" s="11">
-        <f t="shared" ref="D18:E18" si="30">D5/D3</f>
+      <c r="D18" s="9">
+        <f t="shared" ref="D18:E18" si="105">D5/D3</f>
         <v>0.70036298223635607</v>
       </c>
-      <c r="E18" s="11">
-        <f t="shared" si="30"/>
+      <c r="E18" s="9">
+        <f t="shared" si="105"/>
         <v>0.6866512392667925</v>
       </c>
-      <c r="F18" s="11">
-        <f t="shared" ref="F18:J18" si="31">F5/F3</f>
+      <c r="F18" s="9">
+        <f t="shared" ref="F18:L18" si="106">F5/F3</f>
         <v>0.69554345410091123</v>
       </c>
-      <c r="G18" s="11">
-        <f t="shared" si="31"/>
+      <c r="G18" s="9">
+        <f t="shared" si="106"/>
         <v>0.65004019292604498</v>
       </c>
-      <c r="H18" s="11">
-        <f t="shared" si="31"/>
+      <c r="H18" s="9">
+        <f t="shared" si="106"/>
         <v>0.70713077356846255</v>
       </c>
-      <c r="I18" s="11">
-        <f t="shared" si="31"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="J18" s="11">
-        <f t="shared" si="31"/>
+      <c r="I18" s="9">
+        <f t="shared" si="106"/>
+        <v>0.71495360204009362</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="106"/>
+        <v>0.71080073311002967</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="106"/>
+        <v>0.71031963470319637</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="106"/>
+        <v>0.70572874163538435</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" ref="M18:P18" si="107">M5/M3</f>
+        <v>0.7218572708271126</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="107"/>
+        <v>0.72403031654034777</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="107"/>
+        <v>0.70602345415778256</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" ref="P18:Q18" si="108">P5/P3</f>
+        <v>0.69932168014609963</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" si="108"/>
+        <v>0.70674632810555138</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" ref="R18" si="109">R5/R3</f>
         <v>0.7</v>
       </c>
-      <c r="L18" s="11">
-        <f t="shared" ref="L18:X18" si="32">L5/L3</f>
+      <c r="T18" s="9">
+        <f t="shared" ref="T18:AF18" si="110">T5/T3</f>
         <v>0.69966980104255705</v>
       </c>
-      <c r="M18" s="11">
-        <f t="shared" si="32"/>
+      <c r="U18" s="9">
+        <f t="shared" si="110"/>
         <v>0.69130081064590176</v>
       </c>
-      <c r="N18" s="11">
-        <f t="shared" si="32"/>
+      <c r="V18" s="9">
+        <f t="shared" si="110"/>
         <v>0.68489999060944684</v>
       </c>
-      <c r="O18" s="11">
-        <f t="shared" si="32"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="P18" s="11">
-        <f t="shared" si="32"/>
+      <c r="W18" s="9">
+        <f t="shared" si="110"/>
+        <v>0.71275885103540415</v>
+      </c>
+      <c r="X18" s="9">
+        <f t="shared" si="110"/>
+        <v>0.70789519048439919</v>
+      </c>
+      <c r="Y18" s="9">
+        <f t="shared" si="110"/>
+        <v>0.7229463022268563</v>
+      </c>
+      <c r="Z18" s="9">
+        <f t="shared" si="110"/>
+        <v>0.70263678312458799</v>
+      </c>
+      <c r="AA18" s="9">
+        <f t="shared" si="110"/>
         <v>0.7</v>
       </c>
-      <c r="Q18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AB18" s="9">
+        <f t="shared" si="110"/>
         <v>0.7</v>
       </c>
-      <c r="R18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AC18" s="9">
+        <f t="shared" si="110"/>
         <v>0.7</v>
       </c>
-      <c r="S18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AD18" s="9">
+        <f t="shared" si="110"/>
         <v>0.7</v>
       </c>
-      <c r="T18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AE18" s="9">
+        <f t="shared" si="110"/>
         <v>0.7</v>
       </c>
-      <c r="U18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AF18" s="9">
+        <f t="shared" si="110"/>
         <v>0.7</v>
       </c>
-      <c r="V18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AG18" s="9">
+        <f t="shared" ref="AG18:AK18" si="111">AG5/AG3</f>
         <v>0.7</v>
       </c>
-      <c r="W18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AH18" s="9">
+        <f t="shared" si="111"/>
         <v>0.7</v>
       </c>
-      <c r="X18" s="11">
-        <f t="shared" si="32"/>
+      <c r="AI18" s="9">
+        <f t="shared" si="111"/>
         <v>0.7</v>
       </c>
+      <c r="AJ18" s="9">
+        <f t="shared" si="111"/>
+        <v>0.7</v>
+      </c>
+      <c r="AK18" s="9">
+        <f t="shared" si="111"/>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B19" s="10" t="s">
+    <row r="19" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="9">
         <f>C8/C3</f>
         <v>0.36768314055380302</v>
       </c>
-      <c r="D19" s="11">
-        <f t="shared" ref="D19:E19" si="33">D8/D3</f>
+      <c r="D19" s="9">
+        <f t="shared" ref="D19:E19" si="112">D8/D3</f>
         <v>0.34637499598470978</v>
       </c>
-      <c r="E19" s="11">
-        <f t="shared" si="33"/>
+      <c r="E19" s="9">
+        <f t="shared" si="112"/>
         <v>0.34830400097436209</v>
       </c>
-      <c r="F19" s="11">
-        <f t="shared" ref="F19:J19" si="34">F8/F3</f>
+      <c r="F19" s="9">
+        <f t="shared" ref="F19:L19" si="113">F8/F3</f>
         <v>0.33199044232051561</v>
       </c>
-      <c r="G19" s="11">
-        <f t="shared" si="34"/>
+      <c r="G19" s="9">
+        <f t="shared" si="113"/>
         <v>0.21487138263665592</v>
       </c>
-      <c r="H19" s="11">
-        <f t="shared" si="34"/>
+      <c r="H19" s="9">
+        <f t="shared" si="113"/>
         <v>0.37084123647921258</v>
       </c>
-      <c r="I19" s="11">
-        <f t="shared" si="34"/>
-        <v>0.33448918444899167</v>
-      </c>
-      <c r="J19" s="11">
-        <f t="shared" si="34"/>
-        <v>0.37577748010190309</v>
-      </c>
-      <c r="L19" s="11">
-        <f t="shared" ref="L19:X19" si="35">L8/L3</f>
+      <c r="I19" s="9">
+        <f t="shared" si="113"/>
+        <v>0.40655474487025112</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="113"/>
+        <v>0.38113294992521424</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="113"/>
+        <v>0.42100456621004567</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="113"/>
+        <v>0.39040313367063817</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" ref="M19:P19" si="114">M8/M3</f>
+        <v>0.43998208420424006</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="114"/>
+        <v>0.40154554911576756</v>
+      </c>
+      <c r="O19" s="9">
+        <f t="shared" si="114"/>
+        <v>0.41964285714285715</v>
+      </c>
+      <c r="P19" s="9">
+        <f t="shared" ref="P19:Q19" si="115">P8/P3</f>
+        <v>0.39120793112444563</v>
+      </c>
+      <c r="Q19" s="9">
+        <f t="shared" si="115"/>
+        <v>0.41411501120238986</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" ref="R19" si="116">R8/R3</f>
+        <v>0.38490369137923391</v>
+      </c>
+      <c r="T19" s="9">
+        <f t="shared" ref="T19:AF19" si="117">T8/T3</f>
         <v>0.35656458993312212</v>
       </c>
-      <c r="M19" s="11">
-        <f t="shared" si="35"/>
+      <c r="U19" s="9">
+        <f t="shared" si="117"/>
         <v>0.3397739489205916</v>
       </c>
-      <c r="N19" s="11">
-        <f t="shared" si="35"/>
+      <c r="V19" s="9">
+        <f t="shared" si="117"/>
         <v>0.3101073653238175</v>
       </c>
-      <c r="O19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.35832781050011775</v>
-      </c>
-      <c r="P19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.38189140977597164</v>
-      </c>
-      <c r="Q19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.39977452283909626</v>
-      </c>
-      <c r="R19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.41079197154224878</v>
-      </c>
-      <c r="S19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.41817405479357311</v>
-      </c>
-      <c r="T19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.42354216803560035</v>
-      </c>
-      <c r="U19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.4314409632345832</v>
-      </c>
-      <c r="V19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.4366055600954567</v>
-      </c>
-      <c r="W19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.4391627876673454</v>
-      </c>
-      <c r="X19" s="11">
-        <f t="shared" si="35"/>
-        <v>0.44169518778707989</v>
-      </c>
-      <c r="Z19" t="s">
+      <c r="W19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.39311957247828994</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.40484399241510083</v>
+      </c>
+      <c r="Y19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.42071944589260446</v>
+      </c>
+      <c r="Z19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.40527356624917599</v>
+      </c>
+      <c r="AA19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.39607226750561253</v>
+      </c>
+      <c r="AB19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.40467399578375562</v>
+      </c>
+      <c r="AC19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.41311188161850554</v>
+      </c>
+      <c r="AD19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.4186289608181496</v>
+      </c>
+      <c r="AE19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.42136071848010936</v>
+      </c>
+      <c r="AF19" s="9">
+        <f t="shared" si="117"/>
+        <v>0.42406595422302085</v>
+      </c>
+      <c r="AG19" s="9">
+        <f t="shared" ref="AG19:AK19" si="118">AG8/AG3</f>
+        <v>0.42674492554124399</v>
+      </c>
+      <c r="AH19" s="9">
+        <f t="shared" si="118"/>
+        <v>0.4293978874291931</v>
+      </c>
+      <c r="AI19" s="9">
+        <f t="shared" si="118"/>
+        <v>0.43202509240560871</v>
+      </c>
+      <c r="AJ19" s="9">
+        <f t="shared" si="118"/>
+        <v>0.43462679053759307</v>
+      </c>
+      <c r="AK19" s="9">
+        <f t="shared" si="118"/>
+        <v>0.43720322946441259</v>
+      </c>
+      <c r="AM19" t="s">
         <v>33</v>
       </c>
-      <c r="AA19" s="11">
+      <c r="AN19" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B20" s="10" t="s">
+    <row r="20" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="11">
-        <f t="shared" ref="E20" si="36">E6/C6-1</f>
+      <c r="E20" s="9">
+        <f t="shared" ref="E20" si="119">E6/C6-1</f>
         <v>0.15212038303693576</v>
       </c>
-      <c r="F20" s="11">
-        <f t="shared" ref="F20:F21" si="37">F6/D6-1</f>
+      <c r="F20" s="9">
+        <f t="shared" ref="F20:F21" si="120">F6/D6-1</f>
         <v>0.17105738000721771</v>
       </c>
-      <c r="G20" s="11">
-        <f t="shared" ref="G20:G21" si="38">G6/E6-1</f>
+      <c r="G20" s="9">
+        <f t="shared" ref="G20:G21" si="121">G6/E6-1</f>
         <v>-8.7508905248159685E-2</v>
       </c>
-      <c r="H20" s="11">
-        <f t="shared" ref="H20:H21" si="39">H6/F6-1</f>
+      <c r="H20" s="9">
+        <f t="shared" ref="H20:H21" si="122">H6/F6-1</f>
         <v>-4.4684129429892194E-2</v>
       </c>
-      <c r="I20" s="11">
-        <f t="shared" ref="I20:I21" si="40">I6/G6-1</f>
+      <c r="I20" s="9">
+        <f t="shared" ref="I20:I21" si="123">I6/G6-1</f>
+        <v>0.21665582303188025</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" ref="J20:J21" si="124">J6/H6-1</f>
+        <v>0.2924731182795699</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" ref="K20:K21" si="125">K6/I6-1</f>
+        <v>0.25989304812834235</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" ref="L20:L21" si="126">L6/J6-1</f>
+        <v>0.24958402662229617</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" ref="M20:M21" si="127">M6/K6-1</f>
+        <v>0.26061120543293725</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" ref="N20:N21" si="128">N6/L6-1</f>
+        <v>0.12117177097203724</v>
+      </c>
+      <c r="O20" s="9">
+        <f t="shared" ref="O20:O21" si="129">O6/M6-1</f>
+        <v>0.1326599326599327</v>
+      </c>
+      <c r="P20" s="9">
+        <f t="shared" ref="P20:Q21" si="130">P6/N6-1</f>
+        <v>0.12054631828978613</v>
+      </c>
+      <c r="Q20" s="9">
+        <f t="shared" si="130"/>
+        <v>8.9179548156955946E-2</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" ref="R20:R21" si="131">R6/P6-1</f>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" ref="U20:AF20" si="132">U6/T6-1</f>
+        <v>0.1621967611854318</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="132"/>
+        <v>-6.4548108167648888E-2</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="132"/>
+        <v>0.25816897262290261</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="132"/>
+        <v>0.25409452503509589</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="132"/>
+        <v>0.18246268656716413</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="132"/>
+        <v>0.1262227832123699</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" si="132"/>
+        <v>8.432614177640807E-2</v>
+      </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="132"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" si="132"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" si="132"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" si="132"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF20" s="9">
+        <f t="shared" si="132"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AG20" s="9">
+        <f t="shared" ref="AG20:AG21" si="133">AG6/AF6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH20" s="9">
+        <f t="shared" ref="AH20:AH21" si="134">AH6/AG6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AI20" s="9">
+        <f t="shared" ref="AI20:AI21" si="135">AI6/AH6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AJ20" s="9">
+        <f t="shared" ref="AJ20:AJ21" si="136">AJ6/AI6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AK20" s="9">
+        <f t="shared" ref="AK20:AK21" si="137">AK6/AJ6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN20" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="21" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="9">
+        <f t="shared" ref="E21" si="138">E7/C7-1</f>
+        <v>0.2570093457943925</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="120"/>
+        <v>0.23753232360546717</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="121"/>
+        <v>0.16802973977695168</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="122"/>
+        <v>0.14029850746268679</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="123"/>
+        <v>0.18109484404837684</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="124"/>
+        <v>-5.0000000000000155E-2</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="125"/>
+        <v>9.4044731878199839E-2</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="126"/>
+        <v>0.18489942132818959</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="127"/>
+        <v>-7.3891625615764012E-3</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="128"/>
+        <v>0.13023255813953494</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" si="129"/>
+        <v>0.15880893300248133</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="130"/>
+        <v>-2.2633744855967031E-2</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" si="130"/>
+        <v>0.11134903640256955</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="131"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="J20" s="11">
-        <f t="shared" ref="J20:J21" si="41">J6/H6-1</f>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="M20" s="11">
-        <f t="shared" ref="M20:X20" si="42">M6/L6-1</f>
-        <v>0.1621967611854318</v>
-      </c>
-      <c r="N20" s="11">
-        <f t="shared" si="42"/>
-        <v>-6.4548108167648888E-2</v>
-      </c>
-      <c r="O20" s="11">
-        <f t="shared" si="42"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="P20" s="11">
-        <f t="shared" si="42"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="Q20" s="11">
-        <f t="shared" si="42"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="R20" s="11">
-        <f t="shared" si="42"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="S20" s="11">
-        <f t="shared" si="42"/>
+      <c r="U21" s="9">
+        <f t="shared" ref="U21" si="139">U7/T7-1</f>
+        <v>0.24613162781101705</v>
+      </c>
+      <c r="V21" s="9">
+        <f t="shared" ref="V21" si="140">V7/U7-1</f>
+        <v>0.15264900662251657</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" ref="W21" si="141">W7/V7-1</f>
+        <v>5.4294742889974046E-2</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" ref="X21" si="142">X7/W7-1</f>
+        <v>0.13896457765667569</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" ref="Y21" si="143">Y7/X7-1</f>
+        <v>6.3397129186602896E-2</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" ref="Z21" si="144">Z7/Y7-1</f>
+        <v>5.9617547806524174E-2</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" ref="AA21" si="145">AA7/Z7-1</f>
+        <v>0.10562632696390661</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" ref="AB21" si="146">AB7/AA7-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="T20" s="11">
-        <f t="shared" si="42"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="U20" s="11">
-        <f t="shared" si="42"/>
+      <c r="AC21" s="9">
+        <f t="shared" ref="AC21" si="147">AC7/AB7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="V20" s="11">
-        <f t="shared" si="42"/>
+      <c r="AD21" s="9">
+        <f t="shared" ref="AD21" si="148">AD7/AC7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="W20" s="11">
-        <f t="shared" si="42"/>
+      <c r="AE21" s="9">
+        <f t="shared" ref="AE21" si="149">AE7/AD7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="X20" s="11">
-        <f t="shared" si="42"/>
+      <c r="AF21" s="9">
+        <f t="shared" ref="AF21" si="150">AF7/AE7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Z20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA20" s="11">
-        <v>0.06</v>
+      <c r="AG21" s="9">
+        <f t="shared" si="133"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH21" s="9">
+        <f t="shared" si="134"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AI21" s="9">
+        <f t="shared" si="135"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AJ21" s="9">
+        <f t="shared" si="136"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AK21" s="9">
+        <f t="shared" si="137"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN21" s="5">
+        <f>NPV(AN20,AA13:FI13)</f>
+        <v>99028.06411286295</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B21" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="11">
-        <f t="shared" ref="E21" si="43">E7/C7-1</f>
-        <v>0.2570093457943925</v>
-      </c>
-      <c r="F21" s="11">
-        <f t="shared" si="37"/>
-        <v>0.23753232360546717</v>
-      </c>
-      <c r="G21" s="11">
-        <f t="shared" si="38"/>
-        <v>0.16802973977695168</v>
-      </c>
-      <c r="H21" s="11">
-        <f t="shared" si="39"/>
-        <v>0.14029850746268679</v>
-      </c>
-      <c r="I21" s="11">
-        <f t="shared" si="40"/>
-        <v>0.12999999999999989</v>
-      </c>
-      <c r="J21" s="11">
-        <f t="shared" si="41"/>
-        <v>0.12999999999999989</v>
-      </c>
-      <c r="M21" s="11">
-        <f t="shared" ref="M21" si="44">M7/L7-1</f>
-        <v>0.24613162781101705</v>
-      </c>
-      <c r="N21" s="11">
-        <f t="shared" ref="N21" si="45">N7/M7-1</f>
-        <v>0.15264900662251657</v>
-      </c>
-      <c r="O21" s="11">
-        <f t="shared" ref="O21" si="46">O7/N7-1</f>
-        <v>0.12999999999999989</v>
-      </c>
-      <c r="P21" s="11">
-        <f t="shared" ref="P21" si="47">P7/O7-1</f>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="Q21" s="11">
-        <f t="shared" ref="Q21" si="48">Q7/P7-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="R21" s="11">
-        <f t="shared" ref="R21" si="49">R7/Q7-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="S21" s="11">
-        <f t="shared" ref="S21" si="50">S7/R7-1</f>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="T21" s="11">
-        <f t="shared" ref="T21" si="51">T7/S7-1</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="U21" s="11">
-        <f t="shared" ref="U21" si="52">U7/T7-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="V21" s="11">
-        <f t="shared" ref="V21" si="53">V7/U7-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="W21" s="11">
-        <f t="shared" ref="W21" si="54">W7/V7-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="X21" s="11">
-        <f t="shared" ref="X21" si="55">X7/W7-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA21" s="5">
-        <f>NPV(AA20,N13:EV13)</f>
-        <v>54170.800879636503</v>
-      </c>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B22" s="10" t="s">
+    <row r="22" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="9">
         <f>C11/C10</f>
         <v>0.32492725509214354</v>
       </c>
-      <c r="D22" s="11">
-        <f t="shared" ref="D22:X22" si="56">D11/D10</f>
+      <c r="D22" s="9">
+        <f t="shared" ref="D22:AF22" si="151">D11/D10</f>
         <v>0.32595456742387624</v>
       </c>
-      <c r="E22" s="11">
-        <f t="shared" si="56"/>
+      <c r="E22" s="9">
+        <f t="shared" si="151"/>
         <v>0.34001418942887551</v>
       </c>
-      <c r="F22" s="11">
-        <f t="shared" si="56"/>
+      <c r="F22" s="9">
+        <f t="shared" si="151"/>
         <v>0.32172238753719595</v>
       </c>
-      <c r="G22" s="11">
-        <f t="shared" si="56"/>
+      <c r="G22" s="9">
+        <f t="shared" si="151"/>
         <v>0.32715798045602607</v>
       </c>
-      <c r="H22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.30453810934554271</v>
-      </c>
-      <c r="I22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="J22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="L22" s="11">
-        <f t="shared" si="56"/>
+      <c r="H22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.30250133761369719</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.3049916407929304</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.28644472219066025</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.28502202643171803</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.27822410147991544</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" ref="M22:P22" si="152">M11/M10</f>
+        <v>0.27498345466578422</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="152"/>
+        <v>0.28115015974440893</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="152"/>
+        <v>0.28176291793313069</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" ref="P22:Q22" si="153">P11/P10</f>
+        <v>0.29226361031518627</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="153"/>
+        <v>0.35395683453237409</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" ref="R22:R23" si="154">R11/R10</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="151"/>
         <v>0.32544178165093202</v>
       </c>
-      <c r="M22" s="11">
-        <f t="shared" si="56"/>
+      <c r="U22" s="9">
+        <f t="shared" si="151"/>
         <v>0.33080785833847232</v>
       </c>
-      <c r="N22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.31015988666261901</v>
-      </c>
-      <c r="O22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="P22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="Q22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="R22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="S22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="T22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="U22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="V22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="W22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="X22" s="11">
-        <f t="shared" si="56"/>
-        <v>0.33</v>
-      </c>
-      <c r="Z22" t="s">
+      <c r="V22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.30859846959323406</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.29548762736535661</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.28155339805825241</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.27795855454701146</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.28689161872181618</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.32063776761030655</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.3</v>
+      </c>
+      <c r="AC22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.3</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.3</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.3</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" si="151"/>
+        <v>0.3</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" ref="AG22:AK22" si="155">AG11/AG10</f>
+        <v>0.3</v>
+      </c>
+      <c r="AH22" s="9">
+        <f t="shared" si="155"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI22" s="9">
+        <f t="shared" si="155"/>
+        <v>0.3</v>
+      </c>
+      <c r="AJ22" s="9">
+        <f t="shared" si="155"/>
+        <v>0.3</v>
+      </c>
+      <c r="AK22" s="9">
+        <f t="shared" si="155"/>
+        <v>0.3</v>
+      </c>
+      <c r="AM22" t="s">
         <v>36</v>
       </c>
-      <c r="AA22" s="5">
+      <c r="AN22" s="5">
         <f>Main!D8</f>
-        <v>4738.6000000000004</v>
+        <v>10518</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Z23" t="s">
+    <row r="23" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="9">
+        <f>C13/C3</f>
+        <v>0.24745881528215913</v>
+      </c>
+      <c r="D23" s="9">
+        <f t="shared" ref="D23:R23" si="156">D13/D3</f>
+        <v>0.22447078474832163</v>
+      </c>
+      <c r="E23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.22967541562633215</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.21499222049344288</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.1346061093247588</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.26926231609165935</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.27711270099879587</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.26804862120541817</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.29990867579908675</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.28154072139709485</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.33233801134667063</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.3095556546292168</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.31569829424307039</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.29128619879989565</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.27956186208613393</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="156"/>
+        <v>0.29034165070957763</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" ref="T23:AK23" si="157">T13/T3</f>
+        <v>0.23546370325673385</v>
+      </c>
+      <c r="U23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.2219978498997589</v>
+      </c>
+      <c r="V23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.21682787116161134</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.27232242262302381</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.29020858472677125</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.32092053325389142</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.3033618984838497</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.28162845947638471</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.29425824540850959</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.29860207814957568</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.30120212478437058</v>
+      </c>
+      <c r="AE23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.30209082806956761</v>
+      </c>
+      <c r="AF23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.30309008486975647</v>
+      </c>
+      <c r="AG23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.30418377949907371</v>
+      </c>
+      <c r="AH23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.30535785128375137</v>
+      </c>
+      <c r="AI23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.30660003498783767</v>
+      </c>
+      <c r="AJ23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.3078996340026996</v>
+      </c>
+      <c r="AK23" s="9">
+        <f t="shared" si="157"/>
+        <v>0.30924732216505213</v>
+      </c>
+      <c r="AM23" t="s">
         <v>37</v>
       </c>
-      <c r="AA23" s="5">
-        <f>AA21+AA22</f>
-        <v>58909.400879636501</v>
+      <c r="AN23" s="5">
+        <f>AN21+AN22</f>
+        <v>109546.06411286295</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Z24" t="s">
+    <row r="24" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AM24" t="s">
         <v>38</v>
       </c>
-      <c r="AA24" s="4">
-        <f>AA23/X14</f>
-        <v>558.01798709504214</v>
+      <c r="AN24" s="4">
+        <f>AN23/AF14</f>
+        <v>1037.6726511841823</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Z25" t="s">
+    <row r="25" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AM25" t="s">
         <v>39</v>
       </c>
-      <c r="AA25" s="4">
+      <c r="AN25" s="4">
         <f>Main!D3</f>
-        <v>1049.08</v>
+        <v>2071</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Z26" s="1" t="s">
+    <row r="26" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AM26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AA26" s="12">
-        <f>AA24/AA25-1</f>
-        <v>-0.468088241988178</v>
+      <c r="AN26" s="10">
+        <f>AN24/AN25-1</f>
+        <v>-0.49895091685940018</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Z27" t="s">
+    <row r="27" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AM27" t="s">
         <v>41</v>
       </c>
-      <c r="AA27" s="6" t="s">
-        <v>42</v>
+      <c r="AN27" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
